--- a/source_data/SourceData_Fig4.xlsx
+++ b/source_data/SourceData_Fig4.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/breakeven_sweep.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/breakeven_sweep.csv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/results.json; analysis/supervisor_2026_09_20/nh3_cost_mc_summary.json</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json; analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_mc_summary.json</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/promoted_ru_literature_2026_10_05/fig3_literature_points.csv</t>
+          <t>analysis/promoted_ru_literature_2026_10_05/nh3_1_2/fig3_literature_points.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/scaling_reachability.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/scaling_reachability.csv</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/results.json (backward_reachability)</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (backward_reachability)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>analysis/fe_bridge_backward_2026_09_29/activity_lifecycle_certified_boundary.csv</t>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_certified_boundary.csv</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>analysis/fe_bridge_backward_2026_09_29/activity_lifecycle_target_keypoints.csv</t>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_target_keypoints.csv</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>analysis/fe_bridge_backward_2026_09_29/scaling_lifecycle_exact_global_boundary.csv</t>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_global_boundary.csv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>analysis/fe_bridge_backward_2026_09_29/scaling_lifecycle_exact_summary.json</t>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_summary.json</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/breakeven_sweep.csv</t>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/breakeven_sweep.csv</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>27.03445435957026</v>
+        <v>20.68152947181338</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v>0.1258925411794167</v>
       </c>
       <c r="B6" t="n">
-        <v>26.51320687992889</v>
+        <v>20.27592393832591</v>
       </c>
     </row>
     <row r="7">
@@ -743,7 +743,7 @@
         <v>0.1584893192461113</v>
       </c>
       <c r="B7" t="n">
-        <v>25.96288478754388</v>
+        <v>19.88014715116363</v>
       </c>
     </row>
     <row r="8">
@@ -751,7 +751,7 @@
         <v>0.1995262314968879</v>
       </c>
       <c r="B8" t="n">
-        <v>25.45283459461439</v>
+        <v>19.49350670414761</v>
       </c>
     </row>
     <row r="9">
@@ -759,7 +759,7 @@
         <v>0.251188643150958</v>
       </c>
       <c r="B9" t="n">
-        <v>24.94702561874306</v>
+        <v>19.11350855539104</v>
       </c>
     </row>
     <row r="10">
@@ -767,7 +767,7 @@
         <v>0.3162277660168379</v>
       </c>
       <c r="B10" t="n">
-        <v>24.42791318244652</v>
+        <v>18.74157064867888</v>
       </c>
     </row>
     <row r="11">
@@ -775,7 +775,7 @@
         <v>0.3981071705534973</v>
       </c>
       <c r="B11" t="n">
-        <v>23.94244994807282</v>
+        <v>18.37617435734668</v>
       </c>
     </row>
     <row r="12">
@@ -783,7 +783,7 @@
         <v>0.5011872336272724</v>
       </c>
       <c r="B12" t="n">
-        <v>23.45673666618148</v>
+        <v>17.99109222038301</v>
       </c>
     </row>
     <row r="13">
@@ -791,7 +791,7 @@
         <v>0.6309573444801934</v>
       </c>
       <c r="B13" t="n">
-        <v>22.95983932342158</v>
+        <v>17.52888002245339</v>
       </c>
     </row>
     <row r="14">
@@ -799,7 +799,7 @@
         <v>0.7943282347242815</v>
       </c>
       <c r="B14" t="n">
-        <v>22.48991725694379</v>
+        <v>17.09766310684286</v>
       </c>
     </row>
     <row r="15">
@@ -807,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>22.03059478781101</v>
+        <v>16.63274935890281</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>1.258925411794168</v>
       </c>
       <c r="B16" t="n">
-        <v>21.551892740779</v>
+        <v>16.25799711332062</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>1.584893192461114</v>
       </c>
       <c r="B17" t="n">
-        <v>21.13194590461095</v>
+        <v>15.93751554481386</v>
       </c>
     </row>
     <row r="18">
@@ -831,7 +831,7 @@
         <v>1.99526231496888</v>
       </c>
       <c r="B18" t="n">
-        <v>20.72310678855463</v>
+        <v>15.62413719776115</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>2.511886431509581</v>
       </c>
       <c r="B19" t="n">
-        <v>20.32395137199568</v>
+        <v>15.31883354761153</v>
       </c>
     </row>
     <row r="20">
@@ -847,7 +847,7 @@
         <v>3.16227766016838</v>
       </c>
       <c r="B20" t="n">
-        <v>19.93510978532857</v>
+        <v>15.01835483419082</v>
       </c>
     </row>
     <row r="21">
@@ -855,7 +855,7 @@
         <v>3.981071705534973</v>
       </c>
       <c r="B21" t="n">
-        <v>19.55730032899629</v>
+        <v>14.7269216727954</v>
       </c>
     </row>
     <row r="22">
@@ -863,7 +863,7 @@
         <v>5.011872336272725</v>
       </c>
       <c r="B22" t="n">
-        <v>19.19058457087477</v>
+        <v>14.44578980863959</v>
       </c>
     </row>
     <row r="23">
@@ -871,7 +871,7 @@
         <v>6.309573444801933</v>
       </c>
       <c r="B23" t="n">
-        <v>18.82901001060704</v>
+        <v>14.17391164178946</v>
       </c>
     </row>
     <row r="24">
@@ -879,7 +879,7 @@
         <v>7.943282347242818</v>
       </c>
       <c r="B24" t="n">
-        <v>18.44131719479865</v>
+        <v>13.91081955541578</v>
       </c>
     </row>
     <row r="25">
@@ -887,7 +887,7 @@
         <v>10</v>
       </c>
       <c r="B25" t="n">
-        <v>18.05830951768868</v>
+        <v>13.66109278381242</v>
       </c>
     </row>
     <row r="26">
@@ -895,7 +895,7 @@
         <v>12.58925411794168</v>
       </c>
       <c r="B26" t="n">
-        <v>17.68939083048345</v>
+        <v>13.42446624796132</v>
       </c>
     </row>
     <row r="27">
@@ -903,7 +903,7 @@
         <v>15.84893192461114</v>
       </c>
       <c r="B27" t="n">
-        <v>17.33888428438416</v>
+        <v>13.20151888799497</v>
       </c>
     </row>
     <row r="28">
@@ -911,7 +911,7 @@
         <v>19.95262314968881</v>
       </c>
       <c r="B28" t="n">
-        <v>17.00611435411404</v>
+        <v>12.9952244177211</v>
       </c>
     </row>
     <row r="29">
@@ -919,7 +919,7 @@
         <v>25.11886431509582</v>
       </c>
       <c r="B29" t="n">
-        <v>16.68317910622452</v>
+        <v>12.81216465840052</v>
       </c>
     </row>
     <row r="30">
@@ -927,7 +927,7 @@
         <v>31.6227766016838</v>
       </c>
       <c r="B30" t="n">
-        <v>16.42661375084823</v>
+        <v>12.63620058519418</v>
       </c>
     </row>
     <row r="31">
@@ -935,7 +935,7 @@
         <v>39.81071705534973</v>
       </c>
       <c r="B31" t="n">
-        <v>16.22123645786377</v>
+        <v>12.45112941643002</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         <v>50.11872336272725</v>
       </c>
       <c r="B32" t="n">
-        <v>16.03840122040538</v>
+        <v>12.27339809151852</v>
       </c>
     </row>
     <row r="33">
@@ -951,7 +951,7 @@
         <v>63.09573444801936</v>
       </c>
       <c r="B33" t="n">
-        <v>15.87724428819202</v>
+        <v>12.12420584799695</v>
       </c>
     </row>
     <row r="34">
@@ -959,7 +959,7 @@
         <v>79.43282347242821</v>
       </c>
       <c r="B34" t="n">
-        <v>15.73578758873316</v>
+        <v>11.92654810348958</v>
       </c>
     </row>
     <row r="35">
@@ -967,7 +967,7 @@
         <v>100</v>
       </c>
       <c r="B35" t="n">
-        <v>15.61126864336727</v>
+        <v>11.6516211584086</v>
       </c>
     </row>
     <row r="36">
@@ -975,7 +975,7 @@
         <v>125.8925411794168</v>
       </c>
       <c r="B36" t="n">
-        <v>15.50748588591986</v>
+        <v>11.43319407203439</v>
       </c>
     </row>
     <row r="37">
@@ -983,7 +983,7 @@
         <v>158.4893192461114</v>
       </c>
       <c r="B37" t="n">
-        <v>15.4168298705826</v>
+        <v>11.25965147990086</v>
       </c>
     </row>
     <row r="38">
@@ -991,7 +991,7 @@
         <v>199.5262314968881</v>
       </c>
       <c r="B38" t="n">
-        <v>15.29819538432165</v>
+        <v>11.12176639892864</v>
       </c>
     </row>
     <row r="39">
@@ -999,7 +999,7 @@
         <v>251.1886431509582</v>
       </c>
       <c r="B39" t="n">
-        <v>15.12565135011829</v>
+        <v>11.01126614831115</v>
       </c>
     </row>
     <row r="40">
@@ -1007,7 +1007,7 @@
         <v>316.227766016838</v>
       </c>
       <c r="B40" t="n">
-        <v>14.97397121247854</v>
+        <v>10.89864380345705</v>
       </c>
     </row>
     <row r="41">
@@ -1015,7 +1015,7 @@
         <v>398.1071705534973</v>
       </c>
       <c r="B41" t="n">
-        <v>14.84506451358585</v>
+        <v>10.78064998075691</v>
       </c>
     </row>
     <row r="42">
@@ -1023,7 +1023,7 @@
         <v>501.1872336272725</v>
       </c>
       <c r="B42" t="n">
-        <v>14.72797580163504</v>
+        <v>10.60149104742143</v>
       </c>
     </row>
     <row r="43">
@@ -1031,7 +1031,7 @@
         <v>630.9573444801937</v>
       </c>
       <c r="B43" t="n">
-        <v>14.63492224798192</v>
+        <v>10.44390583633159</v>
       </c>
     </row>
     <row r="44">
@@ -1039,7 +1039,7 @@
         <v>794.3282347242822</v>
       </c>
       <c r="B44" t="n">
-        <v>14.54937669116014</v>
+        <v>10.29737661826858</v>
       </c>
     </row>
     <row r="45">
@@ -1047,7 +1047,7 @@
         <v>1000</v>
       </c>
       <c r="B45" t="n">
-        <v>14.42549379650162</v>
+        <v>10.16633211579392</v>
       </c>
     </row>
     <row r="46">
@@ -1055,7 +1055,7 @@
         <v>1258.925411794169</v>
       </c>
       <c r="B46" t="n">
-        <v>14.25404821847427</v>
+        <v>10.062209269483</v>
       </c>
     </row>
     <row r="47">
@@ -1063,7 +1063,7 @@
         <v>1584.893192461114</v>
       </c>
       <c r="B47" t="n">
-        <v>14.10257459489594</v>
+        <v>9.958821109833943</v>
       </c>
     </row>
     <row r="48">
@@ -1071,7 +1071,7 @@
         <v>1995.262314968879</v>
       </c>
       <c r="B48" t="n">
-        <v>13.96779402532536</v>
+        <v>9.843571096480581</v>
       </c>
     </row>
     <row r="49">
@@ -1079,7 +1079,7 @@
         <v>2511.886431509582</v>
       </c>
       <c r="B49" t="n">
-        <v>13.85647155024598</v>
+        <v>9.677946640163924</v>
       </c>
     </row>
     <row r="50">
@@ -1087,7 +1087,7 @@
         <v>3162.277660168379</v>
       </c>
       <c r="B50" t="n">
-        <v>13.7571811276401</v>
+        <v>9.501160522681728</v>
       </c>
     </row>
     <row r="51">
@@ -1095,7 +1095,7 @@
         <v>3981.071705534978</v>
       </c>
       <c r="B51" t="n">
-        <v>13.67444164389729</v>
+        <v>9.360698676033884</v>
       </c>
     </row>
     <row r="52">
@@ -1103,7 +1103,7 @@
         <v>5011.872336272725</v>
       </c>
       <c r="B52" t="n">
-        <v>13.6086953318076</v>
+        <v>9.232450150338233</v>
       </c>
     </row>
     <row r="53">
@@ -1111,7 +1111,7 @@
         <v>6309.573444801943</v>
       </c>
       <c r="B53" t="n">
-        <v>13.43328910134309</v>
+        <v>9.108575990599659</v>
       </c>
     </row>
     <row r="54">
@@ -1119,7 +1119,7 @@
         <v>7943.282347242822</v>
       </c>
       <c r="B54" t="n">
-        <v>13.26383912127762</v>
+        <v>9.010149630500983</v>
       </c>
     </row>
     <row r="55">
@@ -1127,7 +1127,7 @@
         <v>10000</v>
       </c>
       <c r="B55" t="n">
-        <v>13.12079380019681</v>
+        <v>8.931940518320808</v>
       </c>
     </row>
     <row r="56">
@@ -1135,7 +1135,7 @@
         <v>12589.25411794169</v>
       </c>
       <c r="B56" t="n">
-        <v>12.99359218090064</v>
+        <v>8.787066274655471</v>
       </c>
     </row>
     <row r="57">
@@ -1143,7 +1143,7 @@
         <v>15848.93192461114</v>
       </c>
       <c r="B57" t="n">
-        <v>12.89204281615867</v>
+        <v>8.607362821623905</v>
       </c>
     </row>
     <row r="58">
@@ -1151,7 +1151,7 @@
         <v>19952.62314968883</v>
       </c>
       <c r="B58" t="n">
-        <v>12.79513229994551</v>
+        <v>8.464583348015752</v>
       </c>
     </row>
     <row r="59">
@@ -1159,7 +1159,7 @@
         <v>25118.86431509582</v>
       </c>
       <c r="B59" t="n">
-        <v>12.71812747686215</v>
+        <v>8.311219153305228</v>
       </c>
     </row>
     <row r="60">
@@ -1167,7 +1167,7 @@
         <v>31622.77660168379</v>
       </c>
       <c r="B60" t="n">
-        <v>12.56520745138556</v>
+        <v>8.179932401340796</v>
       </c>
     </row>
     <row r="61">
@@ -1175,7 +1175,7 @@
         <v>39810.71705534977</v>
       </c>
       <c r="B61" t="n">
-        <v>12.33709623341335</v>
+        <v>8.075617100081043</v>
       </c>
     </row>
     <row r="62">
@@ -1183,7 +1183,7 @@
         <v>50118.72336272725</v>
       </c>
       <c r="B62" t="n">
-        <v>12.1558603534724</v>
+        <v>7.992729428473057</v>
       </c>
     </row>
     <row r="63">
@@ -1191,7 +1191,7 @@
         <v>63095.73444801943</v>
       </c>
       <c r="B63" t="n">
-        <v>11.94167132575847</v>
+        <v>7.910441616125598</v>
       </c>
     </row>
     <row r="64">
@@ -1199,7 +1199,7 @@
         <v>79432.82347242821</v>
       </c>
       <c r="B64" t="n">
-        <v>11.75991461860015</v>
+        <v>7.829622388955181</v>
       </c>
     </row>
     <row r="65">
@@ -1207,7 +1207,7 @@
         <v>100000</v>
       </c>
       <c r="B65" t="n">
-        <v>11.615503974052</v>
+        <v>7.76540168263892</v>
       </c>
     </row>
     <row r="66">
@@ -1215,7 +1215,7 @@
         <v>125892.5411794169</v>
       </c>
       <c r="B66" t="n">
-        <v>11.50076244195227</v>
+        <v>7.714368325878455</v>
       </c>
     </row>
     <row r="67">
@@ -1223,7 +1223,7 @@
         <v>158489.3192461114</v>
       </c>
       <c r="B67" t="n">
-        <v>11.40959154357537</v>
+        <v>7.673812427051581</v>
       </c>
     </row>
     <row r="68">
@@ -1231,7 +1231,7 @@
         <v>199526.2314968883</v>
       </c>
       <c r="B68" t="n">
-        <v>11.3371466765848</v>
+        <v>7.641581174856134</v>
       </c>
     </row>
     <row r="69">
@@ -1239,7 +1239,7 @@
         <v>251188.6431509582</v>
       </c>
       <c r="B69" t="n">
-        <v>11.27957927415908</v>
+        <v>7.615964292845103</v>
       </c>
     </row>
     <row r="70">
@@ -1247,7 +1247,7 @@
         <v>316227.7660168379</v>
       </c>
       <c r="B70" t="n">
-        <v>11.23383198950372</v>
+        <v>7.595603049318648</v>
       </c>
     </row>
     <row r="71">
@@ -1255,7 +1255,7 @@
         <v>398107.1705534977</v>
       </c>
       <c r="B71" t="n">
-        <v>11.19747600051142</v>
+        <v>7.579417978286149</v>
       </c>
     </row>
     <row r="72">
@@ -1263,7 +1263,7 @@
         <v>501187.2336272725</v>
       </c>
       <c r="B72" t="n">
-        <v>11.16858177216611</v>
+        <v>7.566551463500919</v>
       </c>
     </row>
     <row r="73">
@@ -1271,7 +1271,7 @@
         <v>630957.3444801943</v>
       </c>
       <c r="B73" t="n">
-        <v>11.14561639583944</v>
+        <v>7.556322128956163</v>
       </c>
     </row>
     <row r="74">
@@ -1279,7 +1279,7 @@
         <v>794328.2347242822</v>
       </c>
       <c r="B74" t="n">
-        <v>11.12736203977327</v>
+        <v>7.548188607855211</v>
       </c>
     </row>
     <row r="75">
@@ -1287,7 +1287,7 @@
         <v>1000000</v>
       </c>
       <c r="B75" t="n">
-        <v>11.11285116913685</v>
+        <v>7.541720761407087</v>
       </c>
     </row>
     <row r="78">
@@ -1300,7 +1300,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>source: provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/results.json; analysis/supervisor_2026_09_20/nh3_cost_mc_summary.json</t>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json; analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_mc_summary.json</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>201.2234429878984</v>
+        <v>114.6671254704968</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>15.29170467662114</v>
+        <v>11.51578359717927</v>
       </c>
     </row>
     <row r="83">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22.03059478781101</v>
+        <v>16.63274935890281</v>
       </c>
     </row>
     <row r="84">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.524565113094345</v>
+        <v>1.575275488957531</v>
       </c>
     </row>
     <row r="85">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>70.78151661985564</v>
+        <v>43.51521000190818</v>
       </c>
     </row>
     <row r="86">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>462.0047303614388</v>
+        <v>262.2756002000399</v>
       </c>
     </row>
     <row r="89">
@@ -1386,7 +1386,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>source: analysis/promoted_ru_literature_2026_10_05/fig3_literature_points.csv</t>
+          <t>source: analysis/promoted_ru_literature_2026_10_05/nh3_1_2/fig3_literature_points.csv</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2032,7 +2032,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/closure/scaling_reachability.csv</t>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/scaling_reachability.csv</t>
         </is>
       </c>
     </row>
@@ -2057,1726 +2057,1718 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.565</v>
+        <v>-1.56</v>
       </c>
       <c r="B5" t="n">
-        <v>2347.289391192421</v>
+        <v>2343.737396236784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.56</v>
+        <v>-1.555</v>
       </c>
       <c r="B6" t="n">
-        <v>2071.542068074885</v>
+        <v>2068.610792143321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.555</v>
+        <v>-1.55</v>
       </c>
       <c r="B7" t="n">
-        <v>1827.603114749727</v>
+        <v>1824.948803975279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.55</v>
+        <v>-1.545</v>
       </c>
       <c r="B8" t="n">
-        <v>1611.84783333586</v>
+        <v>1609.095920209335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.545</v>
+        <v>-1.54</v>
       </c>
       <c r="B9" t="n">
-        <v>1420.916975056992</v>
+        <v>1417.886276860604</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.54</v>
+        <v>-1.535</v>
       </c>
       <c r="B10" t="n">
-        <v>1252.017866156608</v>
+        <v>1248.497253500977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.535</v>
+        <v>-1.53</v>
       </c>
       <c r="B11" t="n">
-        <v>1102.523957105854</v>
+        <v>1098.417709711001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-1.53</v>
+        <v>-1.525</v>
       </c>
       <c r="B12" t="n">
-        <v>970.2772510006414</v>
+        <v>965.4716696144708</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.525</v>
+        <v>-1.52</v>
       </c>
       <c r="B13" t="n">
-        <v>853.2414647562549</v>
+        <v>847.7294020043219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-1.52</v>
+        <v>-1.515</v>
       </c>
       <c r="B14" t="n">
-        <v>749.7264457754483</v>
+        <v>743.489583098478</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.515</v>
+        <v>-1.51</v>
       </c>
       <c r="B15" t="n">
-        <v>658.1676848453734</v>
+        <v>651.2865636578831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.51</v>
+        <v>-1.505</v>
       </c>
       <c r="B16" t="n">
-        <v>577.2295117256494</v>
+        <v>569.785280840233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-1.505</v>
+        <v>-1.5</v>
       </c>
       <c r="B17" t="n">
-        <v>505.7212402811677</v>
+        <v>497.8072036887403</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-1.5</v>
+        <v>-1.495</v>
       </c>
       <c r="B18" t="n">
-        <v>442.5749531660691</v>
+        <v>434.3114149765758</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1.495</v>
+        <v>-1.49</v>
       </c>
       <c r="B19" t="n">
-        <v>386.8961441292072</v>
+        <v>378.3777422328575</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.49</v>
+        <v>-1.485</v>
       </c>
       <c r="B20" t="n">
-        <v>337.8177488505813</v>
+        <v>329.1916564857315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.485</v>
+        <v>-1.48</v>
       </c>
       <c r="B21" t="n">
-        <v>294.6667412888692</v>
+        <v>286.0307066633926</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.48</v>
+        <v>-1.475</v>
       </c>
       <c r="B22" t="n">
-        <v>256.7622332174104</v>
+        <v>248.252312174187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1.475</v>
+        <v>-1.47</v>
       </c>
       <c r="B23" t="n">
-        <v>223.5610234876453</v>
+        <v>215.2827966100509</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.47</v>
+        <v>-1.465</v>
       </c>
       <c r="B24" t="n">
-        <v>194.5503514870637</v>
+        <v>186.6076091585729</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.465</v>
+        <v>-1.46</v>
       </c>
       <c r="B25" t="n">
-        <v>169.2656240023996</v>
+        <v>161.7627398761173</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.46</v>
+        <v>-1.455</v>
       </c>
       <c r="B26" t="n">
-        <v>147.3270577334725</v>
+        <v>140.327378392633</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-1.455</v>
+        <v>-1.45</v>
       </c>
       <c r="B27" t="n">
-        <v>128.3293977270218</v>
+        <v>121.9178784147596</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.45</v>
+        <v>-1.445</v>
       </c>
       <c r="B28" t="n">
-        <v>111.9953877283212</v>
+        <v>106.1830611463588</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.445</v>
+        <v>-1.44</v>
       </c>
       <c r="B29" t="n">
-        <v>98.01716557461694</v>
+        <v>92.80081818225833</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.44</v>
+        <v>-1.435</v>
       </c>
       <c r="B30" t="n">
-        <v>86.11313377229155</v>
+        <v>81.47587248999739</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1.435</v>
+        <v>-1.43</v>
       </c>
       <c r="B31" t="n">
-        <v>76.02550820184445</v>
+        <v>71.93845262450029</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.43</v>
+        <v>-1.425</v>
       </c>
       <c r="B32" t="n">
-        <v>67.5187569312013</v>
+        <v>63.94356288251656</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1.425</v>
+        <v>-1.42</v>
       </c>
       <c r="B33" t="n">
-        <v>60.37868873385576</v>
+        <v>57.27051455404681</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.42</v>
+        <v>-1.415</v>
       </c>
       <c r="B34" t="n">
-        <v>54.41190958782216</v>
+        <v>51.72242568882246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-1.415</v>
+        <v>-1.41</v>
       </c>
       <c r="B35" t="n">
-        <v>49.44537548292408</v>
+        <v>47.12548377549497</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.41</v>
+        <v>-1.405</v>
       </c>
       <c r="B36" t="n">
-        <v>45.32582695297111</v>
+        <v>43.32787048359649</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1.405</v>
+        <v>-1.4</v>
       </c>
       <c r="B37" t="n">
-        <v>41.91897562703016</v>
+        <v>40.19834325893321</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.4</v>
+        <v>-1.395</v>
       </c>
       <c r="B38" t="n">
-        <v>39.10840114018472</v>
+        <v>37.62453735902031</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.395</v>
+        <v>-1.39</v>
       </c>
       <c r="B39" t="n">
-        <v>36.79418788952644</v>
+        <v>35.51108820564725</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.39</v>
+        <v>-1.385</v>
       </c>
       <c r="B40" t="n">
-        <v>34.89137531002118</v>
+        <v>33.63884241936874</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.385</v>
+        <v>-1.38</v>
       </c>
       <c r="B41" t="n">
-        <v>33.36997447882972</v>
+        <v>31.96206504433876</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.38</v>
+        <v>-1.375</v>
       </c>
       <c r="B42" t="n">
-        <v>32.09660779781206</v>
+        <v>30.60161524403237</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-1.375</v>
+        <v>-1.37</v>
       </c>
       <c r="B43" t="n">
-        <v>30.80968233410848</v>
+        <v>29.39764314649552</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1.37</v>
+        <v>-1.365</v>
       </c>
       <c r="B44" t="n">
-        <v>29.75361216615504</v>
+        <v>28.28703669155638</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1.365</v>
+        <v>-1.36</v>
       </c>
       <c r="B45" t="n">
-        <v>28.88312959987559</v>
+        <v>27.25681998752706</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.36</v>
+        <v>-1.355</v>
       </c>
       <c r="B46" t="n">
-        <v>28.11132485636231</v>
+        <v>26.29855739718736</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1.355</v>
+        <v>-1.35</v>
       </c>
       <c r="B47" t="n">
-        <v>27.40912590954606</v>
+        <v>25.28004123033313</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.35</v>
+        <v>-1.345</v>
       </c>
       <c r="B48" t="n">
-        <v>26.77138584934607</v>
+        <v>24.25447360977775</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.345</v>
+        <v>-1.34</v>
       </c>
       <c r="B49" t="n">
-        <v>26.19362225154652</v>
+        <v>23.41921079055743</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1.34</v>
+        <v>-1.335</v>
       </c>
       <c r="B50" t="n">
-        <v>25.67144233822622</v>
+        <v>22.7186297693011</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-1.335</v>
+        <v>-1.33</v>
       </c>
       <c r="B51" t="n">
-        <v>25.20103861883412</v>
+        <v>22.07927251552352</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-1.33</v>
+        <v>-1.325</v>
       </c>
       <c r="B52" t="n">
-        <v>24.77849979003396</v>
+        <v>21.49467136034138</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-1.325</v>
+        <v>-1.32</v>
       </c>
       <c r="B53" t="n">
-        <v>24.39979207385317</v>
+        <v>20.96344054283819</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-1.32</v>
+        <v>-1.315</v>
       </c>
       <c r="B54" t="n">
-        <v>24.0611371483979</v>
+        <v>20.48197127903165</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.315</v>
+        <v>-1.31</v>
       </c>
       <c r="B55" t="n">
-        <v>23.75907372177017</v>
+        <v>20.04803208518428</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-1.31</v>
+        <v>-1.305</v>
       </c>
       <c r="B56" t="n">
-        <v>23.40681253981765</v>
+        <v>19.65733997015532</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-1.305</v>
+        <v>-1.3</v>
       </c>
       <c r="B57" t="n">
-        <v>23.08183398274822</v>
+        <v>19.30734870114318</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-1.3</v>
+        <v>-1.295</v>
       </c>
       <c r="B58" t="n">
-        <v>22.80552781242368</v>
+        <v>18.99441737831644</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1.295</v>
+        <v>-1.29</v>
       </c>
       <c r="B59" t="n">
-        <v>22.57026697194958</v>
+        <v>18.71560782783246</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-1.29</v>
+        <v>-1.285</v>
       </c>
       <c r="B60" t="n">
-        <v>22.36974584282539</v>
+        <v>18.46678853457969</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.285</v>
+        <v>-1.28</v>
       </c>
       <c r="B61" t="n">
-        <v>22.19874354598829</v>
+        <v>18.2454214552779</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.28</v>
+        <v>-1.275</v>
       </c>
       <c r="B62" t="n">
-        <v>22.05293030774688</v>
+        <v>18.03371170131477</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-1.275</v>
+        <v>-1.27</v>
       </c>
       <c r="B63" t="n">
-        <v>21.92870924746048</v>
+        <v>17.78066613117084</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1.27</v>
+        <v>-1.265</v>
       </c>
       <c r="B64" t="n">
-        <v>21.82308719405816</v>
+        <v>17.56493948355447</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-1.265</v>
+        <v>-1.26</v>
       </c>
       <c r="B65" t="n">
-        <v>21.73356922877697</v>
+        <v>17.38076680300698</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-1.26</v>
+        <v>-1.255</v>
       </c>
       <c r="B66" t="n">
-        <v>21.65807258400199</v>
+        <v>17.2233792730785</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1.255</v>
+        <v>-1.25</v>
       </c>
       <c r="B67" t="n">
-        <v>21.5948563142796</v>
+        <v>17.08882421766448</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-1.25</v>
+        <v>-1.245</v>
       </c>
       <c r="B68" t="n">
-        <v>21.54246381129808</v>
+        <v>16.97381864423983</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.245</v>
+        <v>-1.24</v>
       </c>
       <c r="B69" t="n">
-        <v>21.49967577707041</v>
+        <v>16.87563009455423</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1.24</v>
+        <v>-1.235</v>
       </c>
       <c r="B70" t="n">
-        <v>21.46547171549882</v>
+        <v>16.79197968561434</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.235</v>
+        <v>-1.23</v>
       </c>
       <c r="B71" t="n">
-        <v>21.43899836737484</v>
+        <v>16.72096316120492</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.23</v>
+        <v>-1.225</v>
       </c>
       <c r="B72" t="n">
-        <v>21.41954381134493</v>
+        <v>16.6609865524388</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.225</v>
+        <v>-1.22</v>
       </c>
       <c r="B73" t="n">
-        <v>21.40651619525832</v>
+        <v>16.61071368673085</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1.22</v>
+        <v>-1.215</v>
       </c>
       <c r="B74" t="n">
-        <v>21.39942625862667</v>
+        <v>16.56902330917486</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-1.215</v>
+        <v>-1.21</v>
       </c>
       <c r="B75" t="n">
-        <v>21.39787296604955</v>
+        <v>16.53497400767677</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1.21</v>
+        <v>-1.205</v>
       </c>
       <c r="B76" t="n">
-        <v>21.40153170034269</v>
+        <v>16.50777548016178</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1.205</v>
+        <v>-1.2</v>
       </c>
       <c r="B77" t="n">
-        <v>21.41014456846948</v>
+        <v>16.48676496312016</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.2</v>
+        <v>-1.195</v>
       </c>
       <c r="B78" t="n">
-        <v>21.42351245789436</v>
+        <v>16.47138786782681</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1.195</v>
+        <v>-1.19</v>
       </c>
       <c r="B79" t="n">
-        <v>21.44148854946051</v>
+        <v>16.46118185386553</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.19</v>
+        <v>-1.185</v>
       </c>
       <c r="B80" t="n">
-        <v>21.46397304843645</v>
+        <v>16.4557637174379</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1.185</v>
+        <v>-1.18</v>
       </c>
       <c r="B81" t="n">
-        <v>21.49090894048539</v>
+        <v>16.45481859115869</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-1.18</v>
+        <v>-1.175</v>
       </c>
       <c r="B82" t="n">
-        <v>21.5222786160024</v>
+        <v>16.45809104818635</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.175</v>
+        <v>-1.17</v>
       </c>
       <c r="B83" t="n">
-        <v>21.5581012361877</v>
+        <v>16.46537778111046</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.17</v>
+        <v>-1.165</v>
       </c>
       <c r="B84" t="n">
-        <v>21.59843073868678</v>
+        <v>16.47652158865393</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.165</v>
+        <v>-1.16</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6433544006991</v>
+        <v>16.49140645388478</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-1.16</v>
+        <v>-1.155</v>
       </c>
       <c r="B86" t="n">
-        <v>21.69299189399692</v>
+        <v>16.50995353862591</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-1.155</v>
+        <v>-1.15</v>
       </c>
       <c r="B87" t="n">
-        <v>21.74749477999499</v>
+        <v>16.53211795200765</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-1.15</v>
+        <v>-1.145</v>
       </c>
       <c r="B88" t="n">
-        <v>21.80704640443233</v>
+        <v>16.5578861781459</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.145</v>
+        <v>-1.14</v>
       </c>
       <c r="B89" t="n">
-        <v>21.87186216082124</v>
+        <v>16.58727406997919</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1.14</v>
+        <v>-1.135</v>
       </c>
       <c r="B90" t="n">
-        <v>21.94219009995639</v>
+        <v>16.62032533434243</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-1.135</v>
+        <v>-1.13</v>
       </c>
       <c r="B91" t="n">
-        <v>22.00968533808427</v>
+        <v>16.65711044818552</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1.13</v>
+        <v>-1.125</v>
       </c>
       <c r="B92" t="n">
-        <v>22.07187333474192</v>
+        <v>16.69772595809812</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.125</v>
+        <v>-1.12</v>
       </c>
       <c r="B93" t="n">
-        <v>22.1380664104276</v>
+        <v>16.74229412549021</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.12</v>
+        <v>-1.115</v>
       </c>
       <c r="B94" t="n">
-        <v>22.20826983735215</v>
+        <v>16.79096288831252</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1.115</v>
+        <v>-1.11</v>
       </c>
       <c r="B95" t="n">
-        <v>22.28395003586043</v>
+        <v>16.84390611742044</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1.11</v>
+        <v>-1.105</v>
       </c>
       <c r="B96" t="n">
-        <v>22.36545992437226</v>
+        <v>16.90132415185476</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1.105</v>
+        <v>-1.1</v>
       </c>
       <c r="B97" t="n">
-        <v>22.45318764693595</v>
+        <v>16.96344460265828</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.1</v>
+        <v>-1.095</v>
       </c>
       <c r="B98" t="n">
-        <v>22.54755900622543</v>
+        <v>17.03052341954486</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-1.095</v>
+        <v>-1.09</v>
       </c>
       <c r="B99" t="n">
-        <v>22.64057400962683</v>
+        <v>17.09806651276294</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1.09</v>
+        <v>-1.085</v>
       </c>
       <c r="B100" t="n">
-        <v>22.72877268007196</v>
+        <v>17.15556740815475</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.085</v>
+        <v>-1.08</v>
       </c>
       <c r="B101" t="n">
-        <v>22.82086521839816</v>
+        <v>17.2175387070144</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-1.08</v>
+        <v>-1.075</v>
       </c>
       <c r="B102" t="n">
-        <v>22.90737934912569</v>
+        <v>17.28427149915935</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-1.075</v>
+        <v>-1.07</v>
       </c>
       <c r="B103" t="n">
-        <v>22.98189942355646</v>
+        <v>17.35608620803816</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-1.07</v>
+        <v>-1.065</v>
       </c>
       <c r="B104" t="n">
-        <v>23.06197273250881</v>
+        <v>17.43333470428649</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-1.065</v>
+        <v>-1.06</v>
       </c>
       <c r="B105" t="n">
-        <v>23.14798025175697</v>
+        <v>17.51640268048319</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-1.06</v>
+        <v>-1.055</v>
       </c>
       <c r="B106" t="n">
-        <v>23.24033878144933</v>
+        <v>17.60571230447666</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-1.055</v>
+        <v>-1.05</v>
       </c>
       <c r="B107" t="n">
-        <v>23.33950374595675</v>
+        <v>17.70172517148384</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-1.05</v>
+        <v>-1.045</v>
       </c>
       <c r="B108" t="n">
-        <v>23.43345532127838</v>
+        <v>17.80494557811424</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-1.045</v>
+        <v>-1.04</v>
       </c>
       <c r="B109" t="n">
-        <v>23.5129470999176</v>
+        <v>17.89476763949873</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-1.04</v>
+        <v>-1.035</v>
       </c>
       <c r="B110" t="n">
-        <v>23.59842673422261</v>
+        <v>17.98424731272843</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-1.035</v>
+        <v>-1.03</v>
       </c>
       <c r="B111" t="n">
-        <v>23.69035775635282</v>
+        <v>18.08060503759432</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-1.03</v>
+        <v>-1.025</v>
       </c>
       <c r="B112" t="n">
-        <v>23.78924611368862</v>
+        <v>18.18439383899728</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-1.025</v>
+        <v>-1.02</v>
       </c>
       <c r="B113" t="n">
-        <v>23.89564393928695</v>
+        <v>18.29621777408005</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-1.02</v>
+        <v>-1.015</v>
       </c>
       <c r="B114" t="n">
-        <v>24.01015370434759</v>
+        <v>18.41673660959133</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-1.015</v>
+        <v>-1.01</v>
       </c>
       <c r="B115" t="n">
-        <v>24.13343278839681</v>
+        <v>18.54667097177341</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-1.01</v>
+        <v>-1.005</v>
       </c>
       <c r="B116" t="n">
-        <v>24.26619850678462</v>
+        <v>18.67329737063049</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-1.005</v>
+        <v>-1</v>
       </c>
       <c r="B117" t="n">
-        <v>24.39423337251118</v>
+        <v>18.78805630300553</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-1</v>
+        <v>-0.995</v>
       </c>
       <c r="B118" t="n">
-        <v>24.50839440447804</v>
+        <v>18.91209230039805</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-0.995</v>
+        <v>-0.99</v>
       </c>
       <c r="B119" t="n">
-        <v>24.62933171533484</v>
+        <v>19.04621197287803</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-0.99</v>
+        <v>-0.985</v>
       </c>
       <c r="B120" t="n">
-        <v>24.75618096694894</v>
+        <v>19.19129813940349</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-0.985</v>
+        <v>-0.98</v>
       </c>
       <c r="B121" t="n">
-        <v>24.89328395412961</v>
+        <v>19.34831722464444</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-0.98</v>
+        <v>-0.975</v>
       </c>
       <c r="B122" t="n">
-        <v>25.04153567054048</v>
+        <v>19.51127679052166</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-0.975</v>
+        <v>-0.97</v>
       </c>
       <c r="B123" t="n">
-        <v>25.20191544840322</v>
+        <v>19.65297237725546</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-0.97</v>
+        <v>-0.965</v>
       </c>
       <c r="B124" t="n">
-        <v>25.3674506680551</v>
+        <v>19.80676779701248</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-0.965</v>
+        <v>-0.96</v>
       </c>
       <c r="B125" t="n">
-        <v>25.51641583061265</v>
+        <v>19.97377416799586</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-0.96</v>
+        <v>-0.955</v>
       </c>
       <c r="B126" t="n">
-        <v>25.67386978667134</v>
+        <v>20.15521103192157</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-0.955</v>
+        <v>-0.95</v>
       </c>
       <c r="B127" t="n">
-        <v>25.839664094813</v>
+        <v>20.35241726757468</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-0.95</v>
+        <v>-0.945</v>
       </c>
       <c r="B128" t="n">
-        <v>26.01239253108055</v>
+        <v>20.53355813644674</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-0.945</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="B129" t="n">
-        <v>26.20006699777556</v>
+        <v>20.71610932593659</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="B130" t="n">
-        <v>26.37940438643054</v>
+        <v>20.9151420951312</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.93</v>
       </c>
       <c r="B131" t="n">
-        <v>26.54921361450157</v>
+        <v>21.1322434931818</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-0.93</v>
+        <v>-0.925</v>
       </c>
       <c r="B132" t="n">
-        <v>26.73201164365846</v>
+        <v>21.36916073257251</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-0.925</v>
+        <v>-0.92</v>
       </c>
       <c r="B133" t="n">
-        <v>26.92265659824263</v>
+        <v>21.586946175283</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-0.92</v>
+        <v>-0.915</v>
       </c>
       <c r="B134" t="n">
-        <v>27.12653208112096</v>
+        <v>21.81206439013749</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-0.915</v>
+        <v>-0.91</v>
       </c>
       <c r="B135" t="n">
-        <v>27.34272644756372</v>
+        <v>22.05850863029747</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-0.91</v>
+        <v>-0.905</v>
       </c>
       <c r="B136" t="n">
-        <v>27.57080156567872</v>
+        <v>22.3284134558203</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-0.905</v>
+        <v>-0.9</v>
       </c>
       <c r="B137" t="n">
-        <v>27.8116720445275</v>
+        <v>22.60205387373056</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-0.9</v>
+        <v>-0.895</v>
       </c>
       <c r="B138" t="n">
-        <v>28.0670232683608</v>
+        <v>22.85075318619222</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-0.895</v>
+        <v>-0.89</v>
       </c>
       <c r="B139" t="n">
-        <v>28.33767001974157</v>
+        <v>23.12231139262597</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-0.89</v>
+        <v>-0.885</v>
       </c>
       <c r="B140" t="n">
-        <v>28.62463796184875</v>
+        <v>23.38347820066341</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-0.885</v>
+        <v>-0.88</v>
       </c>
       <c r="B141" t="n">
-        <v>28.91648271866669</v>
+        <v>23.64841143826853</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-0.88</v>
+        <v>-0.875</v>
       </c>
       <c r="B142" t="n">
-        <v>29.22087254747123</v>
+        <v>23.92880501616717</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-0.875</v>
+        <v>-0.87</v>
       </c>
       <c r="B143" t="n">
-        <v>29.54506537802682</v>
+        <v>24.23743805052775</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-0.87</v>
+        <v>-0.865</v>
       </c>
       <c r="B144" t="n">
-        <v>29.89061848777305</v>
+        <v>24.57730870348895</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-0.865</v>
+        <v>-0.86</v>
       </c>
       <c r="B145" t="n">
-        <v>30.25850235284561</v>
+        <v>24.95174470084832</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>-0.86</v>
+        <v>-0.855</v>
       </c>
       <c r="B146" t="n">
-        <v>30.65044144202595</v>
+        <v>25.36444039577439</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>-0.855</v>
+        <v>-0.85</v>
       </c>
       <c r="B147" t="n">
-        <v>31.06971993485336</v>
+        <v>25.80966161881662</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-0.85</v>
+        <v>-0.845</v>
       </c>
       <c r="B148" t="n">
-        <v>31.52768025590712</v>
+        <v>26.22998106847519</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-0.845</v>
+        <v>-0.84</v>
       </c>
       <c r="B149" t="n">
-        <v>32.03310937535991</v>
+        <v>26.69494853503727</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-0.84</v>
+        <v>-0.835</v>
       </c>
       <c r="B150" t="n">
-        <v>32.59110330076227</v>
+        <v>27.20949397149255</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-0.835</v>
+        <v>-0.83</v>
       </c>
       <c r="B151" t="n">
-        <v>33.20731852962967</v>
+        <v>27.77910563351569</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-0.83</v>
+        <v>-0.825</v>
       </c>
       <c r="B152" t="n">
-        <v>33.88803481213527</v>
+        <v>28.40989442250038</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-0.825</v>
+        <v>-0.82</v>
       </c>
       <c r="B153" t="n">
-        <v>34.64022504518088</v>
+        <v>29.10866574544791</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-0.82</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="B154" t="n">
-        <v>35.39549987268056</v>
+        <v>29.88301273892133</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="B155" t="n">
-        <v>36.14012156269867</v>
+        <v>30.70130387725088</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.805</v>
       </c>
       <c r="B156" t="n">
-        <v>36.94427836307868</v>
+        <v>31.50539475032072</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-0.805</v>
+        <v>-0.8</v>
       </c>
       <c r="B157" t="n">
-        <v>37.81642024093644</v>
+        <v>32.38150723939981</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-0.8</v>
+        <v>-0.795</v>
       </c>
       <c r="B158" t="n">
-        <v>38.76295063812476</v>
+        <v>33.33788851733594</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-0.795</v>
+        <v>-0.79</v>
       </c>
       <c r="B159" t="n">
-        <v>39.79143244451096</v>
+        <v>34.3833367011356</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-0.79</v>
+        <v>-0.785</v>
       </c>
       <c r="B160" t="n">
-        <v>40.91121037187582</v>
+        <v>35.52836438751769</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-0.785</v>
+        <v>-0.78</v>
       </c>
       <c r="B161" t="n">
-        <v>42.13304340999457</v>
+        <v>36.78135425539178</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-0.78</v>
+        <v>-0.775</v>
       </c>
       <c r="B162" t="n">
-        <v>43.46919586252693</v>
+        <v>38.15808623677061</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-0.775</v>
+        <v>-0.77</v>
       </c>
       <c r="B163" t="n">
-        <v>44.93356303377752</v>
+        <v>39.6715008549957</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-0.77</v>
+        <v>-0.765</v>
       </c>
       <c r="B164" t="n">
-        <v>46.54111232927906</v>
+        <v>41.33899943976046</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-0.765</v>
+        <v>-0.76</v>
       </c>
       <c r="B165" t="n">
-        <v>48.32052985000211</v>
+        <v>43.17721091610066</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-0.76</v>
+        <v>-0.755</v>
       </c>
       <c r="B166" t="n">
-        <v>50.30449442471619</v>
+        <v>45.20898610205633</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-0.755</v>
+        <v>-0.75</v>
       </c>
       <c r="B167" t="n">
-        <v>52.51679114195154</v>
+        <v>47.45731585800534</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-0.75</v>
+        <v>-0.745</v>
       </c>
       <c r="B168" t="n">
-        <v>54.98399620143152</v>
+        <v>49.96531688493842</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-0.745</v>
+        <v>-0.74</v>
       </c>
       <c r="B169" t="n">
-        <v>57.73580698843656</v>
+        <v>52.7699289098704</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-0.74</v>
+        <v>-0.735</v>
       </c>
       <c r="B170" t="n">
-        <v>60.78416861498472</v>
+        <v>55.90652610871739</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-0.735</v>
+        <v>-0.73</v>
       </c>
       <c r="B171" t="n">
-        <v>64.0399175977329</v>
+        <v>59.41472968567668</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>-0.73</v>
+        <v>-0.725</v>
       </c>
       <c r="B172" t="n">
-        <v>67.65986473280489</v>
+        <v>63.33892072304632</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-0.725</v>
+        <v>-0.72</v>
       </c>
       <c r="B173" t="n">
-        <v>71.68878233895492</v>
+        <v>67.64644360754237</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-0.72</v>
+        <v>-0.715</v>
       </c>
       <c r="B174" t="n">
-        <v>76.17693304525456</v>
+        <v>72.37378341587284</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-0.715</v>
+        <v>-0.71</v>
       </c>
       <c r="B175" t="n">
-        <v>81.18051209704498</v>
+        <v>77.64791360754643</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-0.71</v>
+        <v>-0.705</v>
       </c>
       <c r="B176" t="n">
-        <v>86.76219619289746</v>
+        <v>83.53788321961788</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-0.705</v>
+        <v>-0.7</v>
       </c>
       <c r="B177" t="n">
-        <v>92.99243359825589</v>
+        <v>90.11903340399364</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>-0.7</v>
+        <v>-0.695</v>
       </c>
       <c r="B178" t="n">
-        <v>99.94999094188562</v>
+        <v>97.47546259607186</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>-0.695</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="B179" t="n">
-        <v>107.7229655517352</v>
+        <v>105.7035614086144</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="B180" t="n">
-        <v>116.4094222018938</v>
+        <v>114.9095665015554</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="B181" t="n">
-        <v>126.1202431868305</v>
+        <v>125.2125605992704</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>-0.68</v>
+        <v>-0.675</v>
       </c>
       <c r="B182" t="n">
-        <v>136.9780006265487</v>
+        <v>136.7477104103261</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>-0.675</v>
+        <v>-0.67</v>
       </c>
       <c r="B183" t="n">
-        <v>149.1213070096993</v>
+        <v>149.6652133663381</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>-0.67</v>
+        <v>-0.665</v>
       </c>
       <c r="B184" t="n">
-        <v>162.7046742999786</v>
+        <v>164.1336245939482</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>-0.665</v>
+        <v>-0.66</v>
       </c>
       <c r="B185" t="n">
-        <v>177.900978228216</v>
+        <v>180.3421085529101</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>-0.66</v>
+        <v>-0.655</v>
       </c>
       <c r="B186" t="n">
-        <v>194.9035537333859</v>
+        <v>198.5029676133406</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>-0.655</v>
+        <v>-0.65</v>
       </c>
       <c r="B187" t="n">
-        <v>213.930446345133</v>
+        <v>218.854481757042</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>-0.65</v>
+        <v>-0.645</v>
       </c>
       <c r="B188" t="n">
-        <v>235.2230122033161</v>
+        <v>241.6614562060458</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>-0.645</v>
+        <v>-0.64</v>
       </c>
       <c r="B189" t="n">
-        <v>259.0544738004896</v>
+        <v>267.2248267945637</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>-0.64</v>
+        <v>-0.635</v>
       </c>
       <c r="B190" t="n">
-        <v>285.7294688055994</v>
+        <v>295.880607009033</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>-0.635</v>
+        <v>-0.63</v>
       </c>
       <c r="B191" t="n">
-        <v>315.5891976886771</v>
+        <v>328.0029065318657</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>-0.63</v>
+        <v>-0.625</v>
       </c>
       <c r="B192" t="n">
-        <v>349.0160265919349</v>
+        <v>364.0165349572172</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>-0.625</v>
+        <v>-0.62</v>
       </c>
       <c r="B193" t="n">
-        <v>386.4384827590695</v>
+        <v>404.3942332081671</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>-0.62</v>
+        <v>-0.615</v>
       </c>
       <c r="B194" t="n">
-        <v>428.336860208612</v>
+        <v>449.6659524143892</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-0.615</v>
+        <v>-0.61</v>
       </c>
       <c r="B195" t="n">
-        <v>475.2495108235303</v>
+        <v>500.4310551555315</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-0.61</v>
+        <v>-0.605</v>
       </c>
       <c r="B196" t="n">
-        <v>527.7793964277431</v>
+        <v>557.3585345697539</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>-0.605</v>
+        <v>-0.6</v>
       </c>
       <c r="B197" t="n">
-        <v>586.6000187874764</v>
+        <v>621.1950995258405</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-0.6</v>
+        <v>-0.595</v>
       </c>
       <c r="B198" t="n">
-        <v>652.4718686132879</v>
+        <v>692.7867605882917</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>-0.595</v>
+        <v>-0.59</v>
       </c>
       <c r="B199" t="n">
-        <v>726.2423485871573</v>
+        <v>773.0796628250218</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-0.59</v>
+        <v>-0.585</v>
       </c>
       <c r="B200" t="n">
-        <v>808.862210265838</v>
+        <v>863.1352411297953</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-0.585</v>
+        <v>-0.58</v>
       </c>
       <c r="B201" t="n">
-        <v>901.4008013698472</v>
+        <v>964.144922770544</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-0.58</v>
+        <v>-0.575</v>
       </c>
       <c r="B202" t="n">
-        <v>1005.050114084627</v>
+        <v>1077.446119778837</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-0.575</v>
+        <v>-0.57</v>
       </c>
       <c r="B203" t="n">
-        <v>1121.155255369985</v>
+        <v>1204.540199845093</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-0.57</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="B204" t="n">
-        <v>1251.216581789502</v>
+        <v>1347.11268230519</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="B205" t="n">
-        <v>1396.921105294601</v>
+        <v>1507.05593685711</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.555</v>
       </c>
       <c r="B206" t="n">
-        <v>1560.163394535641</v>
+        <v>1686.494697672828</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-0.555</v>
+        <v>-0.55</v>
       </c>
       <c r="B207" t="n">
-        <v>1743.054446435976</v>
+        <v>1887.814745088504</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-0.55</v>
+        <v>-0.545</v>
       </c>
       <c r="B208" t="n">
-        <v>1947.98412333543</v>
+        <v>2113.695151658802</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-0.545</v>
+        <v>-0.54</v>
       </c>
       <c r="B209" t="n">
-        <v>2177.615588724711</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="B210" t="n">
-        <v>2434.93830109126</v>
+        <v>2367.144539718151</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>printed values</t>
+        </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="inlineStr">
-        <is>
-          <t>printed values</t>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (backward_reachability)</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>source: provenance/nh3_final_1_1/source_harness/outputs/nh3_final_20260905T134204Z/results.json (backward_reachability)</t>
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B215" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>best cost</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>16.45481859115869</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>best cost</t>
+          <t>best E_N eV</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>21.39787296604955</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>best E_N eV</t>
+          <t>Fe cost</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-1.215</v>
+        <v>11.51578359717927</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Fe cost</t>
+          <t>673 K headroom</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>15.29170467662114</v>
+        <v>1.02277070031183</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>673 K headroom</t>
+          <t>state-specific max gain</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1.089901226752708</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>state-specific max gain</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>2.524565113094345</v>
+        <v>1.575275488957531</v>
       </c>
     </row>
   </sheetData>
@@ -3834,7 +3826,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/fe_bridge_backward_2026_09_29/activity_lifecycle_certified_boundary.csv</t>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_certified_boundary.csv</t>
         </is>
       </c>
     </row>
@@ -3872,27 +3864,27 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>99.695904</v>
+        <v>99.2506645</v>
       </c>
       <c r="C5" t="n">
-        <v>99.54385599999999</v>
+        <v>98.8759967</v>
       </c>
       <c r="D5" t="n">
-        <v>99.391808</v>
+        <v>98.50132889999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.089901226753</v>
+        <v>1.022770700312</v>
       </c>
       <c r="B6" t="n">
-        <v>99.6520281</v>
+        <v>99.2310499</v>
       </c>
       <c r="C6" t="n">
-        <v>99.4780421</v>
+        <v>98.8465748</v>
       </c>
       <c r="D6" t="n">
-        <v>99.30405610000001</v>
+        <v>98.4620998</v>
       </c>
     </row>
     <row r="7">
@@ -3900,13 +3892,13 @@
         <v>1.25</v>
       </c>
       <c r="B7" t="n">
-        <v>99.5738836</v>
+        <v>99.03509219999999</v>
       </c>
       <c r="C7" t="n">
-        <v>99.3608254</v>
+        <v>98.55263840000001</v>
       </c>
       <c r="D7" t="n">
-        <v>99.1477672</v>
+        <v>98.0701845</v>
       </c>
     </row>
     <row r="8">
@@ -3914,69 +3906,69 @@
         <v>1.5</v>
       </c>
       <c r="B8" t="n">
-        <v>99.45176409999999</v>
+        <v>98.8190768</v>
       </c>
       <c r="C8" t="n">
-        <v>99.1776461</v>
+        <v>98.22861520000001</v>
       </c>
       <c r="D8" t="n">
-        <v>98.9035282</v>
+        <v>97.6381536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.75</v>
+        <v>1.575275488958</v>
       </c>
       <c r="B9" t="n">
-        <v>99.3294805</v>
+        <v>98.75395810000001</v>
       </c>
       <c r="C9" t="n">
-        <v>98.99422079999999</v>
+        <v>98.13093720000001</v>
       </c>
       <c r="D9" t="n">
-        <v>98.6589611</v>
+        <v>97.50791629999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="B10" t="n">
-        <v>99.2066509</v>
+        <v>98.60268789999999</v>
       </c>
       <c r="C10" t="n">
-        <v>98.8099764</v>
+        <v>97.9040318</v>
       </c>
       <c r="D10" t="n">
-        <v>98.4133018</v>
+        <v>97.20537569999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>99.0831039</v>
+        <v>98.3859824</v>
       </c>
       <c r="C11" t="n">
-        <v>98.6246558</v>
+        <v>97.57897370000001</v>
       </c>
       <c r="D11" t="n">
-        <v>98.1662077</v>
+        <v>96.7719649</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.524565113094</v>
+        <v>2.25</v>
       </c>
       <c r="B12" t="n">
-        <v>98.94718999999999</v>
+        <v>98.1690059</v>
       </c>
       <c r="C12" t="n">
-        <v>98.420785</v>
+        <v>97.25350880000001</v>
       </c>
       <c r="D12" t="n">
-        <v>97.89438</v>
+        <v>96.3380118</v>
       </c>
     </row>
     <row r="13">
@@ -3984,13 +3976,13 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>98.7113421</v>
+        <v>97.5167776</v>
       </c>
       <c r="C13" t="n">
-        <v>98.0670131</v>
+        <v>96.2751664</v>
       </c>
       <c r="D13" t="n">
-        <v>97.4226841</v>
+        <v>95.0335552</v>
       </c>
     </row>
     <row r="16">
@@ -4003,7 +3995,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>source: analysis/fe_bridge_backward_2026_09_29/activity_lifecycle_target_keypoints.csv</t>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_target_keypoints.csv</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4024,7 @@
         <v>0.99</v>
       </c>
       <c r="C19" t="n">
-        <v>2.417935792</v>
+        <v>1.290645757</v>
       </c>
     </row>
     <row r="20">
@@ -4043,7 +4035,7 @@
         <v>0.99</v>
       </c>
       <c r="C20" t="n">
-        <v>1.742128785</v>
+        <v>0.903973414</v>
       </c>
     </row>
     <row r="21">
@@ -4054,7 +4046,7 @@
         <v>0.99</v>
       </c>
       <c r="C21" t="n">
-        <v>1.401288815</v>
+        <v>0.710093177</v>
       </c>
     </row>
   </sheetData>
@@ -4112,7 +4104,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/fe_bridge_backward_2026_09_29/scaling_lifecycle_exact_global_boundary.csv</t>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_global_boundary.csv</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4125,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>99.77965827300528</v>
+        <v>99.58744856913955</v>
       </c>
     </row>
     <row r="5">
@@ -4141,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>99.55931654601056</v>
+        <v>99.17489713827914</v>
       </c>
     </row>
     <row r="6">
@@ -4149,7 +4141,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>99.33897481901582</v>
+        <v>98.7623457074187</v>
       </c>
     </row>
     <row r="7">
@@ -4157,7 +4149,7 @@
         <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>99.1186330920211</v>
+        <v>98.34979427655828</v>
       </c>
     </row>
     <row r="8">
@@ -4165,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="B8" t="n">
-        <v>98.89829136502637</v>
+        <v>97.93724284569784</v>
       </c>
     </row>
     <row r="9">
@@ -4173,7 +4165,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="n">
-        <v>98.67794963803163</v>
+        <v>97.52469141483742</v>
       </c>
     </row>
     <row r="10">
@@ -4181,7 +4173,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="n">
-        <v>98.2372661840422</v>
+        <v>96.69958855311656</v>
       </c>
     </row>
     <row r="11">
@@ -4189,7 +4181,7 @@
         <v>50</v>
       </c>
       <c r="B11" t="n">
-        <v>97.79658273005276</v>
+        <v>95.87448569139571</v>
       </c>
     </row>
     <row r="14">
@@ -4202,7 +4194,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>source: analysis/fe_bridge_backward_2026_09_29/scaling_lifecycle_exact_summary.json</t>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_summary.json</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4237,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07078320489516088</v>
+        <v>-0.3167362919996659</v>
       </c>
     </row>
     <row r="20">
@@ -4255,7 +4247,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.36248788151631</v>
+        <v>11.1990473051796</v>
       </c>
     </row>
     <row r="21">
@@ -4265,7 +4257,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>99.1186330920211</v>
+        <v>98.34979427655827</v>
       </c>
     </row>
     <row r="22">
@@ -4275,7 +4267,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.6920251020802</v>
+        <v>12.11970102629835</v>
       </c>
     </row>
     <row r="23">
@@ -4285,7 +4277,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0004406834539894502</v>
+        <v>0.0008251028617208592</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_Fig4.xlsx
+++ b/source_data/SourceData_Fig4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>actual Ru catalyst points</t>
+          <t>marked points: model Ru price and Ru priced as Fe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -620,7 +620,11 @@
           <t>figures/composite/fig2/nh3_1_2/fig2_ru_actual_cost_points.csv</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ru priced as Fe: the 8 USD/kg row of the sweep</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -630,34 +634,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ru/C catalyst's own bed (squares: 8 wt% Ru, 490 kg m-3; bars: 5-10 wt% Ru, 430-550 kg m-3)</t>
+          <t>Fe optimum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>figures/composite/fig2/nh3_1_2/fig2_ru_bed_sensitivity.csv</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>lower panel: alpha_star_supported_bed</t>
-        </is>
-      </c>
+          <t>figures/composite/fig2/nh3_1_2/fig2_pressure_envelopes.csv</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fe optimum</t>
+          <t>waterfall Fe -&gt; Ru</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>figures/composite/fig2/nh3_1_2/fig2_pressure_envelopes.csv</t>
+          <t>analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_decomposition.csv</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>waterfall Fe -&gt; Ru</t>
+          <t>totals</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -683,17 +683,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>totals</t>
+          <t>1,000 descriptor draws</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_decomposition.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/mc_draws.csv</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -706,12 +706,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1,000 descriptor draws</t>
+          <t>Fe bed-feasibility interval and canonical point</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/mc_draws.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/mc_draws.csv + provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (deterministic) + provenance/discover_v1/source_harness/DISCOVER_TASK_V1.json (descriptor_E_N_eV, price_USD_kg)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -719,17 +719,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fe bed-feasibility interval and canonical point</t>
+          <t>decision endpoints (% of 1,000 draws)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/mc_draws.csv + provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (deterministic) + provenance/discover_v1/source_harness/DISCOVER_TASK_V1.json (descriptor_E_N_eV, price_USD_kg)</t>
+          <t>analysis/supervisor_2026_09_20/nh3_1_2/f3_panel_summary.csv</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -737,17 +737,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>h</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>decision endpoints (% of 1,000 draws)</t>
+          <t>Ru - Fe cost gap, 5,000 joint cost draws</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_1_2/f3_panel_summary.csv</t>
+          <t>analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_mc_histogram.csv</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -760,33 +760,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ru - Fe cost gap, 5,000 joint cost draws</t>
+          <t>lines</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_mc_histogram.csv</t>
+          <t>analysis/supervisor_2026_09_20/nh3_1_2/f3_panel_summary.csv</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>lines</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>analysis/supervisor_2026_09_20/nh3_1_2/f3_panel_summary.csv</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18612,7 +18594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O323"/>
+  <dimension ref="A1:O266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22136,7 +22118,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>actual Ru catalyst points</t>
+          <t>marked points: model Ru price and Ru priced as Fe</t>
         </is>
       </c>
     </row>
@@ -22148,2761 +22130,173 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="inlineStr">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Ru priced as Fe: the 8 USD/kg row of the sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B258" s="1" t="inlineStr">
+      <c r="B259" s="1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="C258" s="1" t="inlineStr">
+      <c r="C259" s="1" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D258" s="1" t="inlineStr">
+      <c r="D259" s="1" t="inlineStr">
         <is>
           <t>recovery</t>
         </is>
       </c>
-      <c r="E258" s="1" t="inlineStr">
+      <c r="E259" s="1" t="inlineStr">
         <is>
           <t>p_eff_USD_kg</t>
         </is>
       </c>
-      <c r="F258" s="1" t="inlineStr">
+      <c r="F259" s="1" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="G258" s="1" t="inlineStr">
+      <c r="G259" s="1" t="inlineStr">
         <is>
           <t>gap_to_Fe</t>
         </is>
       </c>
-      <c r="H258" s="1" t="inlineStr">
+      <c r="H259" s="1" t="inlineStr">
         <is>
           <t>alpha_star</t>
         </is>
       </c>
-      <c r="I258" s="1" t="inlineStr">
+      <c r="I259" s="1" t="inlineStr">
         <is>
           <t>T_C</t>
         </is>
       </c>
-      <c r="J258" s="1" t="inlineStr">
+      <c r="J259" s="1" t="inlineStr">
         <is>
           <t>P_bar</t>
         </is>
       </c>
-      <c r="K258" s="1" t="inlineStr">
+      <c r="K259" s="1" t="inlineStr">
         <is>
           <t>Tsep_C</t>
         </is>
       </c>
-      <c r="L258" s="1" t="inlineStr">
+      <c r="L259" s="1" t="inlineStr">
         <is>
           <t>V_m3_benchmark</t>
         </is>
       </c>
-      <c r="M258" s="1" t="inlineStr">
+      <c r="M259" s="1" t="inlineStr">
         <is>
           <t>metal_cost</t>
         </is>
       </c>
-      <c r="N258" s="1" t="inlineStr">
+      <c r="N259" s="1" t="inlineStr">
         <is>
           <t>Fe_same_loop_cost</t>
         </is>
       </c>
-      <c r="O258" s="1" t="inlineStr">
+      <c r="O259" s="1" t="inlineStr">
         <is>
           <t>gap_to_Fe_same_loop</t>
         </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>pure</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Pure Ru, benchmark formulation (canonical)</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>1</v>
-      </c>
-      <c r="D259" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" t="n">
-        <v>53852.5</v>
-      </c>
-      <c r="F259" t="n">
-        <v>16.63274935890281</v>
-      </c>
-      <c r="G259" t="n">
-        <v>5.11696576172354</v>
-      </c>
-      <c r="H259" t="n">
-        <v>114.6671254704968</v>
-      </c>
-      <c r="I259" t="n">
-        <v>450</v>
-      </c>
-      <c r="J259" t="n">
-        <v>220</v>
-      </c>
-      <c r="K259" t="n">
-        <v>30</v>
-      </c>
-      <c r="L259" t="n">
-        <v>0.06552620293244051</v>
-      </c>
-      <c r="M259" t="n">
-        <v>1.819328776517021</v>
-      </c>
-      <c r="N259" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="O259" t="n">
-        <v>5.11696576172354</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>supported</t>
+          <t>pure</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Supported Ru/C, no recovery</t>
+          <t>Pure Ru, benchmark formulation (canonical)</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
       </c>
       <c r="E260" t="n">
-        <v>4895.681818181818</v>
+        <v>53852.5</v>
       </c>
       <c r="F260" t="n">
-        <v>13.57820568662265</v>
+        <v>16.63274935890281</v>
       </c>
       <c r="G260" t="n">
-        <v>2.062422089443386</v>
+        <v>5.11696576172354</v>
       </c>
       <c r="H260" t="n">
-        <v>10.54540637715114</v>
+        <v>114.6671254704968</v>
       </c>
       <c r="I260" t="n">
         <v>450</v>
       </c>
       <c r="J260" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="K260" t="n">
         <v>30</v>
       </c>
       <c r="L260" t="n">
-        <v>0.3761667888989039</v>
+        <v>0.06552620293244051</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9494759114906171</v>
+        <v>1.819328776517021</v>
       </c>
       <c r="N260" t="n">
         <v>11.51578359717927</v>
       </c>
       <c r="O260" t="n">
-        <v>2.062422089443386</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Supported Ru/C, 90% recovery</t>
-        </is>
-      </c>
-      <c r="C261" t="n">
-        <v>11</v>
-      </c>
-      <c r="D261" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E261" t="n">
-        <v>489.5681818181818</v>
-      </c>
-      <c r="F261" t="n">
-        <v>11.68511369241819</v>
-      </c>
-      <c r="G261" t="n">
-        <v>0.1693300952389229</v>
-      </c>
-      <c r="H261" t="n">
-        <v>1.185321796131689</v>
-      </c>
-      <c r="I261" t="n">
-        <v>425</v>
-      </c>
-      <c r="J261" t="n">
-        <v>110</v>
-      </c>
-      <c r="K261" t="n">
-        <v>30</v>
-      </c>
-      <c r="L261" t="n">
-        <v>3.817530590292625</v>
-      </c>
-      <c r="M261" t="n">
-        <v>0.963576116719741</v>
-      </c>
-      <c r="N261" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="O261" t="n">
-        <v>0.1693300952389229</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Supported Ru/C, 95.55% recovery</t>
-        </is>
-      </c>
-      <c r="C262" t="n">
-        <v>11</v>
-      </c>
-      <c r="D262" t="n">
-        <v>0.9555</v>
-      </c>
-      <c r="E262" t="n">
-        <v>217.8578409090908</v>
-      </c>
-      <c r="F262" t="n">
-        <v>11.15032894763873</v>
-      </c>
-      <c r="G262" t="n">
-        <v>-0.3654546495405331</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0.5988875194764584</v>
-      </c>
-      <c r="I262" t="n">
-        <v>425</v>
-      </c>
-      <c r="J262" t="n">
-        <v>110</v>
-      </c>
-      <c r="K262" t="n">
-        <v>30</v>
-      </c>
-      <c r="L262" t="n">
-        <v>3.817530590292625</v>
-      </c>
-      <c r="M262" t="n">
-        <v>0.4287913719402846</v>
-      </c>
-      <c r="N262" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="O262" t="n">
-        <v>-0.3654546495405331</v>
+        <v>5.11696576172354</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Supported Ru/C, 90% recovery, KAAP loop (90 bar, Tsep -20 C)</t>
-        </is>
-      </c>
-      <c r="C263" t="n">
-        <v>11</v>
-      </c>
-      <c r="D263" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E263" t="n">
-        <v>489.5681818181818</v>
-      </c>
-      <c r="F263" t="n">
-        <v>16.39086820385656</v>
-      </c>
-      <c r="G263" t="n">
-        <v>4.875084606677289</v>
-      </c>
-      <c r="H263" t="n">
-        <v/>
-      </c>
-      <c r="I263" t="n">
-        <v>400</v>
-      </c>
-      <c r="J263" t="n">
-        <v>90</v>
-      </c>
-      <c r="K263" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L263" t="n">
-        <v>0.3614711920350161</v>
-      </c>
-      <c r="M263" t="n">
-        <v>0.0912383016426485</v>
-      </c>
-      <c r="N263" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="O263" t="n">
-        <v>-0.588700644148993</v>
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Fe optimum</t>
+        </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Supported Ru/C, 95.55% recovery, KAAP loop (90 bar, Tsep -20 C)</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>11</v>
-      </c>
-      <c r="D264" t="n">
-        <v>0.9555</v>
-      </c>
-      <c r="E264" t="n">
-        <v>217.8578409090908</v>
-      </c>
-      <c r="F264" t="n">
-        <v>16.2728065463168</v>
-      </c>
-      <c r="G264" t="n">
-        <v>4.757022949137534</v>
-      </c>
-      <c r="H264" t="n">
-        <v/>
-      </c>
-      <c r="I264" t="n">
-        <v>375</v>
-      </c>
-      <c r="J264" t="n">
-        <v>90</v>
-      </c>
-      <c r="K264" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L264" t="n">
-        <v>0.9616871942197392</v>
-      </c>
-      <c r="M264" t="n">
-        <v>0.1080183017879304</v>
-      </c>
-      <c r="N264" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="O264" t="n">
-        <v>-0.7067623016887481</v>
+          <t>source: figures/composite/fig2/nh3_1_2/fig2_pressure_envelopes.csv</t>
+        </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>fe_kaap</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Fe (fused iron), KAAP loop (90 bar, Tsep -20 C)</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" t="n">
-        <v>8</v>
-      </c>
-      <c r="F265" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="G265" t="n">
-        <v>5.463785250826282</v>
-      </c>
-      <c r="I265" t="n">
-        <v>450</v>
-      </c>
-      <c r="J265" t="n">
-        <v>90</v>
-      </c>
-      <c r="K265" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L265" t="n">
-        <v>5.824834105081329</v>
-      </c>
-      <c r="M265" t="n">
-        <v>0.02402502591806</v>
-      </c>
-      <c r="N265" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="O265" t="n">
-        <v>0</v>
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>strict_scaling_reach</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Strict-scaling reach: scaling-consistent Ru matches Fe at or below this p_eff</t>
-        </is>
-      </c>
-      <c r="E266" t="n">
-        <v>444.3385186082257</v>
-      </c>
-      <c r="F266" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="G266" t="n">
-        <v>0</v>
-      </c>
-      <c r="I266" t="n">
-        <v>425</v>
-      </c>
-      <c r="J266" t="n">
-        <v>110</v>
-      </c>
-      <c r="K266" t="n">
-        <v>30</v>
-      </c>
-      <c r="L266" t="n">
-        <v>3.508979648705241</v>
-      </c>
-      <c r="N266" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="O266" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="1" t="inlineStr">
-        <is>
-          <t>Ru/C catalyst's own bed (squares: 8 wt% Ru, 490 kg m-3; bars: 5-10 wt% Ru, 430-550 kg m-3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>source: figures/composite/fig2/nh3_1_2/fig2_ru_bed_sensitivity.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>lower panel: alpha_star_supported_bed</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B272" s="1" t="inlineStr">
-        <is>
-          <t>w_Ru</t>
-        </is>
-      </c>
-      <c r="C272" s="1" t="inlineStr">
-        <is>
-          <t>rho_bed_kg_m3</t>
-        </is>
-      </c>
-      <c r="D272" s="1" t="inlineStr">
-        <is>
-          <t>bed_factor</t>
-        </is>
-      </c>
-      <c r="E272" s="1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="F272" s="1" t="inlineStr">
-        <is>
-          <t>delta_vs_benchmark_bed</t>
-        </is>
-      </c>
-      <c r="G272" s="1" t="inlineStr">
-        <is>
-          <t>T_C</t>
-        </is>
-      </c>
-      <c r="H272" s="1" t="inlineStr">
-        <is>
-          <t>P_bar</t>
-        </is>
-      </c>
-      <c r="I272" s="1" t="inlineStr">
-        <is>
-          <t>Tsep_C</t>
-        </is>
-      </c>
-      <c r="J272" s="1" t="inlineStr">
-        <is>
-          <t>V_m3</t>
-        </is>
-      </c>
-      <c r="K272" s="1" t="inlineStr">
-        <is>
-          <t>Fe_reference</t>
-        </is>
-      </c>
-      <c r="L272" s="1" t="inlineStr">
-        <is>
-          <t>Fe_reference_cost</t>
-        </is>
-      </c>
-      <c r="M272" s="1" t="inlineStr">
-        <is>
-          <t>gap_to_Fe_reference</t>
-        </is>
-      </c>
-      <c r="N272" s="1" t="inlineStr">
-        <is>
-          <t>alpha_star_supported_bed</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C273" t="n">
-        <v>430</v>
-      </c>
-      <c r="D273" t="n">
-        <v>7.559196617336151</v>
-      </c>
-      <c r="E273" t="n">
-        <v>13.69365636208672</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0.1154506754640714</v>
-      </c>
-      <c r="G273" t="n">
-        <v>450</v>
-      </c>
-      <c r="H273" t="n">
-        <v>150</v>
-      </c>
-      <c r="I273" t="n">
-        <v>30</v>
-      </c>
-      <c r="J273" t="n">
-        <v>2.843518718198796</v>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L273" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M273" t="n">
-        <v>2.177872764907457</v>
-      </c>
-      <c r="N273" t="n">
-        <v>11.52849747729072</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C274" t="n">
-        <v>490</v>
-      </c>
-      <c r="D274" t="n">
-        <v>6.633580705009276</v>
-      </c>
-      <c r="E274" t="n">
-        <v>13.67877183446779</v>
-      </c>
-      <c r="F274" t="n">
-        <v>0.1005661478451358</v>
-      </c>
-      <c r="G274" t="n">
-        <v>450</v>
-      </c>
-      <c r="H274" t="n">
-        <v>150</v>
-      </c>
-      <c r="I274" t="n">
-        <v>30</v>
-      </c>
-      <c r="J274" t="n">
-        <v>2.495332752705067</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L274" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M274" t="n">
-        <v>2.162988237288522</v>
-      </c>
-      <c r="N274" t="n">
-        <v>11.4029416245776</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C275" t="n">
-        <v>550</v>
-      </c>
-      <c r="D275" t="n">
-        <v>5.909917355371901</v>
-      </c>
-      <c r="E275" t="n">
-        <v>13.66699931673394</v>
-      </c>
-      <c r="F275" t="n">
-        <v>0.0887936301112848</v>
-      </c>
-      <c r="G275" t="n">
-        <v>450</v>
-      </c>
-      <c r="H275" t="n">
-        <v>150</v>
-      </c>
-      <c r="I275" t="n">
-        <v>30</v>
-      </c>
-      <c r="J275" t="n">
-        <v>2.22311463422815</v>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L275" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M275" t="n">
-        <v>2.151215719554671</v>
-      </c>
-      <c r="N275" t="n">
-        <v>11.30345776612843</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C276" t="n">
-        <v>430</v>
-      </c>
-      <c r="D276" t="n">
-        <v>4.724497885835096</v>
-      </c>
-      <c r="E276" t="n">
-        <v>13.64736202586527</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.069156339242614</v>
-      </c>
-      <c r="G276" t="n">
-        <v>450</v>
-      </c>
-      <c r="H276" t="n">
-        <v>150</v>
-      </c>
-      <c r="I276" t="n">
-        <v>30</v>
-      </c>
-      <c r="J276" t="n">
-        <v>1.777199198874248</v>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L276" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M276" t="n">
-        <v>2.131578428686</v>
-      </c>
-      <c r="N276" t="n">
-        <v>11.13712434612573</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C277" t="n">
-        <v>490</v>
-      </c>
-      <c r="D277" t="n">
-        <v>4.145987940630798</v>
-      </c>
-      <c r="E277" t="n">
-        <v>13.63756340195641</v>
-      </c>
-      <c r="F277" t="n">
-        <v>0.0593577153337534</v>
-      </c>
-      <c r="G277" t="n">
-        <v>450</v>
-      </c>
-      <c r="H277" t="n">
-        <v>150</v>
-      </c>
-      <c r="I277" t="n">
-        <v>30</v>
-      </c>
-      <c r="J277" t="n">
-        <v>1.559582970440667</v>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L277" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M277" t="n">
-        <v>2.121779804777139</v>
-      </c>
-      <c r="N277" t="n">
-        <v>11.05392339366594</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B278" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C278" t="n">
-        <v>550</v>
-      </c>
-      <c r="D278" t="n">
-        <v>3.693698347107438</v>
-      </c>
-      <c r="E278" t="n">
-        <v>13.6297709850515</v>
-      </c>
-      <c r="F278" t="n">
-        <v>0.0515652984288443</v>
-      </c>
-      <c r="G278" t="n">
-        <v>450</v>
-      </c>
-      <c r="H278" t="n">
-        <v>150</v>
-      </c>
-      <c r="I278" t="n">
-        <v>30</v>
-      </c>
-      <c r="J278" t="n">
-        <v>1.389446646392594</v>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L278" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M278" t="n">
-        <v>2.11398738787223</v>
-      </c>
-      <c r="N278" t="n">
-        <v>10.98764698307101</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C279" t="n">
-        <v>430</v>
-      </c>
-      <c r="D279" t="n">
-        <v>3.779598308668076</v>
-      </c>
-      <c r="E279" t="n">
-        <v>13.63126111849788</v>
-      </c>
-      <c r="F279" t="n">
-        <v>0.0530554318752258</v>
-      </c>
-      <c r="G279" t="n">
-        <v>450</v>
-      </c>
-      <c r="H279" t="n">
-        <v>150</v>
-      </c>
-      <c r="I279" t="n">
-        <v>30</v>
-      </c>
-      <c r="J279" t="n">
-        <v>1.421759359099398</v>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L279" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M279" t="n">
-        <v>2.115477521318612</v>
-      </c>
-      <c r="N279" t="n">
-        <v>11.00032900289568</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C280" t="n">
-        <v>490</v>
-      </c>
-      <c r="D280" t="n">
-        <v>3.316790352504638</v>
-      </c>
-      <c r="E280" t="n">
-        <v>13.62316835779647</v>
-      </c>
-      <c r="F280" t="n">
-        <v>0.0449626711738186</v>
-      </c>
-      <c r="G280" t="n">
-        <v>450</v>
-      </c>
-      <c r="H280" t="n">
-        <v>150</v>
-      </c>
-      <c r="I280" t="n">
-        <v>30</v>
-      </c>
-      <c r="J280" t="n">
-        <v>1.247666376352533</v>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L280" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M280" t="n">
-        <v>2.107384760617204</v>
-      </c>
-      <c r="N280" t="n">
-        <v>10.93140522131901</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>supported</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C281" t="n">
-        <v>550</v>
-      </c>
-      <c r="D281" t="n">
-        <v>2.95495867768595</v>
-      </c>
-      <c r="E281" t="n">
-        <v>13.61671644829003</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0.0385107616673732</v>
-      </c>
-      <c r="G281" t="n">
-        <v>450</v>
-      </c>
-      <c r="H281" t="n">
-        <v>150</v>
-      </c>
-      <c r="I281" t="n">
-        <v>30</v>
-      </c>
-      <c r="J281" t="n">
-        <v>1.111557317114075</v>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L281" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M281" t="n">
-        <v>2.100932851110759</v>
-      </c>
-      <c r="N281" t="n">
-        <v>10.87636411709808</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C282" t="n">
-        <v>430</v>
-      </c>
-      <c r="D282" t="n">
-        <v>7.559196617336151</v>
-      </c>
-      <c r="E282" t="n">
-        <v>12.19947327384561</v>
-      </c>
-      <c r="F282" t="n">
-        <v>0.5143595814274242</v>
-      </c>
-      <c r="G282" t="n">
-        <v>450</v>
-      </c>
-      <c r="H282" t="n">
-        <v>110</v>
-      </c>
-      <c r="I282" t="n">
-        <v>25</v>
-      </c>
-      <c r="J282" t="n">
-        <v>9.346024378116145</v>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L282" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M282" t="n">
-        <v>0.6836896766663472</v>
-      </c>
-      <c r="N282" t="n">
-        <v>2.024891099875838</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B283" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C283" t="n">
-        <v>490</v>
-      </c>
-      <c r="D283" t="n">
-        <v>6.633580705009276</v>
-      </c>
-      <c r="E283" t="n">
-        <v>12.16478478647511</v>
-      </c>
-      <c r="F283" t="n">
-        <v>0.479671094056922</v>
-      </c>
-      <c r="G283" t="n">
-        <v>450</v>
-      </c>
-      <c r="H283" t="n">
-        <v>110</v>
-      </c>
-      <c r="I283" t="n">
-        <v>25</v>
-      </c>
-      <c r="J283" t="n">
-        <v>8.201613229775392</v>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L283" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M283" t="n">
-        <v>0.6490011892958449</v>
-      </c>
-      <c r="N283" t="n">
-        <v>1.905851860635627</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B284" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C284" t="n">
-        <v>550</v>
-      </c>
-      <c r="D284" t="n">
-        <v>5.909917355371901</v>
-      </c>
-      <c r="E284" t="n">
-        <v>12.1227647856472</v>
-      </c>
-      <c r="F284" t="n">
-        <v>0.4376510932290092</v>
-      </c>
-      <c r="G284" t="n">
-        <v>450</v>
-      </c>
-      <c r="H284" t="n">
-        <v>110</v>
-      </c>
-      <c r="I284" t="n">
-        <v>30</v>
-      </c>
-      <c r="J284" t="n">
-        <v>11.82933428321039</v>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L284" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M284" t="n">
-        <v>0.6069811884679321</v>
-      </c>
-      <c r="N284" t="n">
-        <v>1.812989879616585</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C285" t="n">
-        <v>430</v>
-      </c>
-      <c r="D285" t="n">
-        <v>4.724497885835096</v>
-      </c>
-      <c r="E285" t="n">
-        <v>12.05050001705874</v>
-      </c>
-      <c r="F285" t="n">
-        <v>0.3653863246405464</v>
-      </c>
-      <c r="G285" t="n">
-        <v>450</v>
-      </c>
-      <c r="H285" t="n">
-        <v>110</v>
-      </c>
-      <c r="I285" t="n">
-        <v>30</v>
-      </c>
-      <c r="J285" t="n">
-        <v>9.456589906636214</v>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L285" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M285" t="n">
-        <v>0.5347164198794694</v>
-      </c>
-      <c r="N285" t="n">
-        <v>1.661307609244767</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C286" t="n">
-        <v>490</v>
-      </c>
-      <c r="D286" t="n">
-        <v>4.145987940630798</v>
-      </c>
-      <c r="E286" t="n">
-        <v>12.01539520646665</v>
-      </c>
-      <c r="F286" t="n">
-        <v>0.3302815140484636</v>
-      </c>
-      <c r="G286" t="n">
-        <v>450</v>
-      </c>
-      <c r="H286" t="n">
-        <v>110</v>
-      </c>
-      <c r="I286" t="n">
-        <v>30</v>
-      </c>
-      <c r="J286" t="n">
-        <v>8.298640122150147</v>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L286" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M286" t="n">
-        <v>0.4996116092873865</v>
-      </c>
-      <c r="N286" t="n">
-        <v>1.587487352310318</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B287" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C287" t="n">
-        <v>550</v>
-      </c>
-      <c r="D287" t="n">
-        <v>3.693698347107438</v>
-      </c>
-      <c r="E287" t="n">
-        <v>11.98797857251976</v>
-      </c>
-      <c r="F287" t="n">
-        <v>0.3028648801015752</v>
-      </c>
-      <c r="G287" t="n">
-        <v>450</v>
-      </c>
-      <c r="H287" t="n">
-        <v>110</v>
-      </c>
-      <c r="I287" t="n">
-        <v>30</v>
-      </c>
-      <c r="J287" t="n">
-        <v>7.393333927006494</v>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L287" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M287" t="n">
-        <v>0.4721949753404981</v>
-      </c>
-      <c r="N287" t="n">
-        <v>1.529861323652963</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C288" t="n">
-        <v>430</v>
-      </c>
-      <c r="D288" t="n">
-        <v>3.779598308668076</v>
-      </c>
-      <c r="E288" t="n">
-        <v>11.99318549275481</v>
-      </c>
-      <c r="F288" t="n">
-        <v>0.3080718003366236</v>
-      </c>
-      <c r="G288" t="n">
-        <v>450</v>
-      </c>
-      <c r="H288" t="n">
-        <v>110</v>
-      </c>
-      <c r="I288" t="n">
-        <v>30</v>
-      </c>
-      <c r="J288" t="n">
-        <v>7.56527192530897</v>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L288" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M288" t="n">
-        <v>0.4774018955755466</v>
-      </c>
-      <c r="N288" t="n">
-        <v>1.540800360338768</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B289" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C289" t="n">
-        <v>490</v>
-      </c>
-      <c r="D289" t="n">
-        <v>3.316790352504638</v>
-      </c>
-      <c r="E289" t="n">
-        <v>11.95455239737001</v>
-      </c>
-      <c r="F289" t="n">
-        <v>0.2694387049518223</v>
-      </c>
-      <c r="G289" t="n">
-        <v>425</v>
-      </c>
-      <c r="H289" t="n">
-        <v>110</v>
-      </c>
-      <c r="I289" t="n">
-        <v>30</v>
-      </c>
-      <c r="J289" t="n">
-        <v>12.66194863227392</v>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L289" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M289" t="n">
-        <v>0.4387688001907452</v>
-      </c>
-      <c r="N289" t="n">
-        <v>1.48188918154751</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>supp_rec90</t>
-        </is>
-      </c>
-      <c r="B290" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C290" t="n">
-        <v>550</v>
-      </c>
-      <c r="D290" t="n">
-        <v>2.95495867768595</v>
-      </c>
-      <c r="E290" t="n">
-        <v>11.91228489036079</v>
-      </c>
-      <c r="F290" t="n">
-        <v>0.2271711979425994</v>
-      </c>
-      <c r="G290" t="n">
-        <v>425</v>
-      </c>
-      <c r="H290" t="n">
-        <v>110</v>
-      </c>
-      <c r="I290" t="n">
-        <v>30</v>
-      </c>
-      <c r="J290" t="n">
-        <v>11.28064514511676</v>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L290" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M290" t="n">
-        <v>0.3965012931815224</v>
-      </c>
-      <c r="N290" t="n">
-        <v>1.435864218496343</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B291" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C291" t="n">
-        <v>430</v>
-      </c>
-      <c r="D291" t="n">
-        <v>7.559196617336151</v>
-      </c>
-      <c r="E291" t="n">
-        <v>11.93700465488536</v>
-      </c>
-      <c r="F291" t="n">
-        <v>0.7866757072466299</v>
-      </c>
-      <c r="G291" t="n">
-        <v>425</v>
-      </c>
-      <c r="H291" t="n">
-        <v>110</v>
-      </c>
-      <c r="I291" t="n">
-        <v>30</v>
-      </c>
-      <c r="J291" t="n">
-        <v>28.85746432471729</v>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L291" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M291" t="n">
-        <v>0.4212210577060968</v>
-      </c>
-      <c r="N291" t="n">
-        <v>1.445177470704388</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C292" t="n">
-        <v>490</v>
-      </c>
-      <c r="D292" t="n">
-        <v>6.633580705009276</v>
-      </c>
-      <c r="E292" t="n">
-        <v>11.82051227763336</v>
-      </c>
-      <c r="F292" t="n">
-        <v>0.6701833299946252</v>
-      </c>
-      <c r="G292" t="n">
-        <v>425</v>
-      </c>
-      <c r="H292" t="n">
-        <v>110</v>
-      </c>
-      <c r="I292" t="n">
-        <v>30</v>
-      </c>
-      <c r="J292" t="n">
-        <v>25.32389726454783</v>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L292" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M292" t="n">
-        <v>0.304728680454092</v>
-      </c>
-      <c r="N292" t="n">
-        <v>1.324662100011353</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B293" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C293" t="n">
-        <v>550</v>
-      </c>
-      <c r="D293" t="n">
-        <v>5.909917355371901</v>
-      </c>
-      <c r="E293" t="n">
-        <v>11.73086985110493</v>
-      </c>
-      <c r="F293" t="n">
-        <v>0.5805409034662006</v>
-      </c>
-      <c r="G293" t="n">
-        <v>425</v>
-      </c>
-      <c r="H293" t="n">
-        <v>110</v>
-      </c>
-      <c r="I293" t="n">
-        <v>30</v>
-      </c>
-      <c r="J293" t="n">
-        <v>22.56129029023352</v>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L293" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M293" t="n">
-        <v>0.2150862539256675</v>
-      </c>
-      <c r="N293" t="n">
-        <v>1.230578106460055</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B294" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C294" t="n">
-        <v>430</v>
-      </c>
-      <c r="D294" t="n">
-        <v>4.724497885835096</v>
-      </c>
-      <c r="E294" t="n">
-        <v>11.58673972485196</v>
-      </c>
-      <c r="F294" t="n">
-        <v>0.4364107772132257</v>
-      </c>
-      <c r="G294" t="n">
-        <v>425</v>
-      </c>
-      <c r="H294" t="n">
-        <v>110</v>
-      </c>
-      <c r="I294" t="n">
-        <v>30</v>
-      </c>
-      <c r="J294" t="n">
-        <v>18.03591520294831</v>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L294" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M294" t="n">
-        <v>0.0709561276726926</v>
-      </c>
-      <c r="N294" t="n">
-        <v>1.076808703196341</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C295" t="n">
-        <v>490</v>
-      </c>
-      <c r="D295" t="n">
-        <v>4.145987940630798</v>
-      </c>
-      <c r="E295" t="n">
-        <v>11.51759671367697</v>
-      </c>
-      <c r="F295" t="n">
-        <v>0.3672677660382337</v>
-      </c>
-      <c r="G295" t="n">
-        <v>425</v>
-      </c>
-      <c r="H295" t="n">
-        <v>110</v>
-      </c>
-      <c r="I295" t="n">
-        <v>30</v>
-      </c>
-      <c r="J295" t="n">
-        <v>15.8274357903424</v>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L295" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M295" t="n">
-        <v>0.0018131164977006</v>
-      </c>
-      <c r="N295" t="n">
-        <v>1.001971309484999</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C296" t="n">
-        <v>550</v>
-      </c>
-      <c r="D296" t="n">
-        <v>3.693698347107438</v>
-      </c>
-      <c r="E296" t="n">
-        <v>11.4640582136776</v>
-      </c>
-      <c r="F296" t="n">
-        <v>0.3137292660388677</v>
-      </c>
-      <c r="G296" t="n">
-        <v>425</v>
-      </c>
-      <c r="H296" t="n">
-        <v>110</v>
-      </c>
-      <c r="I296" t="n">
-        <v>30</v>
-      </c>
-      <c r="J296" t="n">
-        <v>14.10080643139595</v>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L296" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M296" t="n">
-        <v>-0.0517253835016653</v>
-      </c>
-      <c r="N296" t="n">
-        <v>0.9435821699923728</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B297" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C297" t="n">
-        <v>430</v>
-      </c>
-      <c r="D297" t="n">
-        <v>3.779598308668076</v>
-      </c>
-      <c r="E297" t="n">
-        <v>11.47419270863564</v>
-      </c>
-      <c r="F297" t="n">
-        <v>0.3238637609969057</v>
-      </c>
-      <c r="G297" t="n">
-        <v>425</v>
-      </c>
-      <c r="H297" t="n">
-        <v>110</v>
-      </c>
-      <c r="I297" t="n">
-        <v>30</v>
-      </c>
-      <c r="J297" t="n">
-        <v>14.42873216235865</v>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L297" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M297" t="n">
-        <v>-0.0415908885436273</v>
-      </c>
-      <c r="N297" t="n">
-        <v>0.9546625540121726</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B298" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C298" t="n">
-        <v>490</v>
-      </c>
-      <c r="D298" t="n">
-        <v>3.316790352504638</v>
-      </c>
-      <c r="E298" t="n">
-        <v>11.41976765259055</v>
-      </c>
-      <c r="F298" t="n">
-        <v>0.2694387049518205</v>
-      </c>
-      <c r="G298" t="n">
-        <v>425</v>
-      </c>
-      <c r="H298" t="n">
-        <v>110</v>
-      </c>
-      <c r="I298" t="n">
-        <v>30</v>
-      </c>
-      <c r="J298" t="n">
-        <v>12.66194863227392</v>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L298" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M298" t="n">
-        <v>-0.0960159445887125</v>
-      </c>
-      <c r="N298" t="n">
-        <v>0.8950192102437444</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>supp_rec_hi</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C299" t="n">
-        <v>550</v>
-      </c>
-      <c r="D299" t="n">
-        <v>2.95495867768595</v>
-      </c>
-      <c r="E299" t="n">
-        <v>11.37750014558133</v>
-      </c>
-      <c r="F299" t="n">
-        <v>0.2271711979425994</v>
-      </c>
-      <c r="G299" t="n">
-        <v>425</v>
-      </c>
-      <c r="H299" t="n">
-        <v>110</v>
-      </c>
-      <c r="I299" t="n">
-        <v>30</v>
-      </c>
-      <c r="J299" t="n">
-        <v>11.28064514511676</v>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-      <c r="L299" t="n">
-        <v>11.51578359717927</v>
-      </c>
-      <c r="M299" t="n">
-        <v>-0.1382834515979336</v>
-      </c>
-      <c r="N299" t="n">
-        <v>0.8484913968774207</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C300" t="n">
-        <v>430</v>
-      </c>
-      <c r="D300" t="n">
-        <v>7.559196617336151</v>
-      </c>
-      <c r="E300" t="n">
-        <v>16.46365004721098</v>
-      </c>
-      <c r="F300" t="n">
-        <v>0.07278184335442001</v>
-      </c>
-      <c r="G300" t="n">
-        <v>400</v>
-      </c>
-      <c r="H300" t="n">
-        <v>90</v>
-      </c>
-      <c r="I300" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J300" t="n">
-        <v>2.73243181209556</v>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L300" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M300" t="n">
-        <v>-0.515918800794573</v>
-      </c>
-      <c r="N300" t="n">
-        <v>0.1440889384149303</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C301" t="n">
-        <v>490</v>
-      </c>
-      <c r="D301" t="n">
-        <v>6.633580705009276</v>
-      </c>
-      <c r="E301" t="n">
-        <v>16.45454563577325</v>
-      </c>
-      <c r="F301" t="n">
-        <v>0.06367743191669099</v>
-      </c>
-      <c r="G301" t="n">
-        <v>400</v>
-      </c>
-      <c r="H301" t="n">
-        <v>90</v>
-      </c>
-      <c r="I301" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J301" t="n">
-        <v>2.397848324900186</v>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L301" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M301" t="n">
-        <v>-0.525023212232302</v>
-      </c>
-      <c r="N301" t="n">
-        <v>0.1365189416051749</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C302" t="n">
-        <v>550</v>
-      </c>
-      <c r="D302" t="n">
-        <v>5.909917355371901</v>
-      </c>
-      <c r="E302" t="n">
-        <v>16.44730579049365</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0.0564375866370916</v>
-      </c>
-      <c r="G302" t="n">
-        <v>400</v>
-      </c>
-      <c r="H302" t="n">
-        <v>90</v>
-      </c>
-      <c r="I302" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J302" t="n">
-        <v>2.136264871274711</v>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L302" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M302" t="n">
-        <v>-0.5322630575119014</v>
-      </c>
-      <c r="N302" t="n">
-        <v>0.1305953008682714</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C303" t="n">
-        <v>430</v>
-      </c>
-      <c r="D303" t="n">
-        <v>4.724497885835096</v>
-      </c>
-      <c r="E303" t="n">
-        <v>16.43513974325197</v>
-      </c>
-      <c r="F303" t="n">
-        <v>0.0442715393954102</v>
-      </c>
-      <c r="G303" t="n">
-        <v>400</v>
-      </c>
-      <c r="H303" t="n">
-        <v>90</v>
-      </c>
-      <c r="I303" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J303" t="n">
-        <v>1.707769882559726</v>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L303" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M303" t="n">
-        <v>-0.5444291047535827</v>
-      </c>
-      <c r="N303" t="n">
-        <v>0.1208716875727468</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B304" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C304" t="n">
-        <v>490</v>
-      </c>
-      <c r="D304" t="n">
-        <v>4.145987940630798</v>
-      </c>
-      <c r="E304" t="n">
-        <v>16.42902033808826</v>
-      </c>
-      <c r="F304" t="n">
-        <v>0.038152134231705</v>
-      </c>
-      <c r="G304" t="n">
-        <v>400</v>
-      </c>
-      <c r="H304" t="n">
-        <v>90</v>
-      </c>
-      <c r="I304" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J304" t="n">
-        <v>1.498655203062616</v>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L304" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M304" t="n">
-        <v>-0.550548509917288</v>
-      </c>
-      <c r="N304" t="n">
-        <v>0.1161101513175733</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C305" t="n">
-        <v>550</v>
-      </c>
-      <c r="D305" t="n">
-        <v>3.693698347107438</v>
-      </c>
-      <c r="E305" t="n">
-        <v>16.42412689606546</v>
-      </c>
-      <c r="F305" t="n">
-        <v>0.033258692208907</v>
-      </c>
-      <c r="G305" t="n">
-        <v>400</v>
-      </c>
-      <c r="H305" t="n">
-        <v>90</v>
-      </c>
-      <c r="I305" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J305" t="n">
-        <v>1.335165544546694</v>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L305" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M305" t="n">
-        <v>-0.5554419519400859</v>
-      </c>
-      <c r="N305" t="n">
-        <v>0.1123752438369377</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C306" t="n">
-        <v>430</v>
-      </c>
-      <c r="D306" t="n">
-        <v>3.779598308668076</v>
-      </c>
-      <c r="E306" t="n">
-        <v>16.42506464221257</v>
-      </c>
-      <c r="F306" t="n">
-        <v>0.0341964383560124</v>
-      </c>
-      <c r="G306" t="n">
-        <v>400</v>
-      </c>
-      <c r="H306" t="n">
-        <v>90</v>
-      </c>
-      <c r="I306" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J306" t="n">
-        <v>1.36621590604778</v>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L306" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M306" t="n">
-        <v>-0.5545042057929805</v>
-      </c>
-      <c r="N306" t="n">
-        <v>0.1130856185264922</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C307" t="n">
-        <v>490</v>
-      </c>
-      <c r="D307" t="n">
-        <v>3.316790352504638</v>
-      </c>
-      <c r="E307" t="n">
-        <v>16.41995979666035</v>
-      </c>
-      <c r="F307" t="n">
-        <v>0.0290915928037911</v>
-      </c>
-      <c r="G307" t="n">
-        <v>400</v>
-      </c>
-      <c r="H307" t="n">
-        <v>90</v>
-      </c>
-      <c r="I307" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J307" t="n">
-        <v>1.198924162450093</v>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L307" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M307" t="n">
-        <v>-0.5596090513452019</v>
-      </c>
-      <c r="N307" t="n">
-        <v>0.109251244859434</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>kaap90</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C308" t="n">
-        <v>550</v>
-      </c>
-      <c r="D308" t="n">
-        <v>2.95495867768595</v>
-      </c>
-      <c r="E308" t="n">
-        <v>16.41586742948259</v>
-      </c>
-      <c r="F308" t="n">
-        <v>0.0249992256260327</v>
-      </c>
-      <c r="G308" t="n">
-        <v>400</v>
-      </c>
-      <c r="H308" t="n">
-        <v>90</v>
-      </c>
-      <c r="I308" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J308" t="n">
-        <v>1.068132435637356</v>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L308" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M308" t="n">
-        <v>-0.5637014185229603</v>
-      </c>
-      <c r="N308" t="n">
-        <v>0.1062387539788867</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C309" t="n">
-        <v>430</v>
-      </c>
-      <c r="D309" t="n">
-        <v>7.559196617336151</v>
-      </c>
-      <c r="E309" t="n">
-        <v>16.41301278979931</v>
-      </c>
-      <c r="F309" t="n">
-        <v>0.1402062434825062</v>
-      </c>
-      <c r="G309" t="n">
-        <v>400</v>
-      </c>
-      <c r="H309" t="n">
-        <v>90</v>
-      </c>
-      <c r="I309" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J309" t="n">
-        <v>2.73243181209556</v>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L309" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M309" t="n">
-        <v>-0.5665560582062419</v>
-      </c>
-      <c r="N309" t="n">
-        <v>0.0984308579500507</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C310" t="n">
-        <v>490</v>
-      </c>
-      <c r="D310" t="n">
-        <v>6.633580705009276</v>
-      </c>
-      <c r="E310" t="n">
-        <v>16.40390837836157</v>
-      </c>
-      <c r="F310" t="n">
-        <v>0.1311018320447736</v>
-      </c>
-      <c r="G310" t="n">
-        <v>400</v>
-      </c>
-      <c r="H310" t="n">
-        <v>90</v>
-      </c>
-      <c r="I310" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J310" t="n">
-        <v>2.397848324900186</v>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L310" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M310" t="n">
-        <v>-0.5756604696439744</v>
-      </c>
-      <c r="N310" t="n">
-        <v>0.0908543074852196</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C311" t="n">
-        <v>550</v>
-      </c>
-      <c r="D311" t="n">
-        <v>5.909917355371901</v>
-      </c>
-      <c r="E311" t="n">
-        <v>16.39666853308198</v>
-      </c>
-      <c r="F311" t="n">
-        <v>0.1238619867651777</v>
-      </c>
-      <c r="G311" t="n">
-        <v>400</v>
-      </c>
-      <c r="H311" t="n">
-        <v>90</v>
-      </c>
-      <c r="I311" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J311" t="n">
-        <v>2.136264871274711</v>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L311" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M311" t="n">
-        <v>-0.5829003149235703</v>
-      </c>
-      <c r="N311" t="n">
-        <v>0.0849337836083963</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B312" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C312" t="n">
-        <v>430</v>
-      </c>
-      <c r="D312" t="n">
-        <v>4.724497885835096</v>
-      </c>
-      <c r="E312" t="n">
-        <v>16.37145948106223</v>
-      </c>
-      <c r="F312" t="n">
-        <v>0.0986529347454308</v>
-      </c>
-      <c r="G312" t="n">
-        <v>375</v>
-      </c>
-      <c r="H312" t="n">
-        <v>90</v>
-      </c>
-      <c r="I312" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J312" t="n">
-        <v>4.543489115925843</v>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L312" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M312" t="n">
-        <v>-0.6081093669433173</v>
-      </c>
-      <c r="N312" t="n">
-        <v>0.0752410100702193</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B313" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C313" t="n">
-        <v>490</v>
-      </c>
-      <c r="D313" t="n">
-        <v>4.145987940630798</v>
-      </c>
-      <c r="E313" t="n">
-        <v>16.35711067807734</v>
-      </c>
-      <c r="F313" t="n">
-        <v>0.08430413176053971</v>
-      </c>
-      <c r="G313" t="n">
-        <v>375</v>
-      </c>
-      <c r="H313" t="n">
-        <v>90</v>
-      </c>
-      <c r="I313" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J313" t="n">
-        <v>3.987143509894107</v>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L313" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M313" t="n">
-        <v>-0.6224581699282083</v>
-      </c>
-      <c r="N313" t="n">
-        <v>0.0705126133581873</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B314" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C314" t="n">
-        <v>550</v>
-      </c>
-      <c r="D314" t="n">
-        <v>3.693698347107438</v>
-      </c>
-      <c r="E314" t="n">
-        <v>16.34577403602889</v>
-      </c>
-      <c r="F314" t="n">
-        <v>0.07296748971209149</v>
-      </c>
-      <c r="G314" t="n">
-        <v>375</v>
-      </c>
-      <c r="H314" t="n">
-        <v>90</v>
-      </c>
-      <c r="I314" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J314" t="n">
-        <v>3.55218239972384</v>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L314" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M314" t="n">
-        <v>-0.6337948119766565</v>
-      </c>
-      <c r="N314" t="n">
-        <v>0.0668159989276271</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B315" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C315" t="n">
-        <v>430</v>
-      </c>
-      <c r="D315" t="n">
-        <v>3.779598308668076</v>
-      </c>
-      <c r="E315" t="n">
-        <v>16.34793662007095</v>
-      </c>
-      <c r="F315" t="n">
-        <v>0.0751300737541527</v>
-      </c>
-      <c r="G315" t="n">
-        <v>375</v>
-      </c>
-      <c r="H315" t="n">
-        <v>90</v>
-      </c>
-      <c r="I315" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J315" t="n">
-        <v>3.634791292740674</v>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L315" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M315" t="n">
-        <v>-0.6316322279345954</v>
-      </c>
-      <c r="N315" t="n">
-        <v>0.0675180998164186</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B316" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C316" t="n">
-        <v>490</v>
-      </c>
-      <c r="D316" t="n">
-        <v>3.316790352504638</v>
-      </c>
-      <c r="E316" t="n">
-        <v>16.33622324586238</v>
-      </c>
-      <c r="F316" t="n">
-        <v>0.0634166995455771</v>
-      </c>
-      <c r="G316" t="n">
-        <v>375</v>
-      </c>
-      <c r="H316" t="n">
-        <v>90</v>
-      </c>
-      <c r="I316" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J316" t="n">
-        <v>3.189714807915285</v>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L316" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M316" t="n">
-        <v>-0.6433456021431709</v>
-      </c>
-      <c r="N316" t="n">
-        <v>0.0637348800373579</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>kaap_hi</t>
-        </is>
-      </c>
-      <c r="B317" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C317" t="n">
-        <v>550</v>
-      </c>
-      <c r="D317" t="n">
-        <v>2.95495867768595</v>
-      </c>
-      <c r="E317" t="n">
-        <v>16.32694205523205</v>
-      </c>
-      <c r="F317" t="n">
-        <v>0.0541355089152517</v>
-      </c>
-      <c r="G317" t="n">
-        <v>375</v>
-      </c>
-      <c r="H317" t="n">
-        <v>90</v>
-      </c>
-      <c r="I317" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J317" t="n">
-        <v>2.841745919779072</v>
-      </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>Fe in the KAAP loop</t>
-        </is>
-      </c>
-      <c r="L317" t="n">
-        <v>16.97956884800555</v>
-      </c>
-      <c r="M317" t="n">
-        <v>-0.6526267927734963</v>
-      </c>
-      <c r="N317" t="n">
-        <v>0.0607755988075925</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="inlineStr">
-        <is>
-          <t>Fe optimum</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>source: figures/composite/fig2/nh3_1_2/fig2_pressure_envelopes.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B322" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
           <t>Fe cost USD/t</t>
         </is>
       </c>
-      <c r="B323" t="n">
+      <c r="B266" t="n">
         <v>11.51578359717927</v>
       </c>
     </row>
